--- a/data/de-escalation training dataset.xlsx
+++ b/data/de-escalation training dataset.xlsx
@@ -8,15 +8,16 @@
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="synthesis_dataset"/>
-    <sheet r:id="rId2" sheetId="2" name="de_escalation_evaluation"/>
-    <sheet r:id="rId3" sheetId="3" name="role_playing_evaluation"/>
+    <sheet r:id="rId2" sheetId="2" name="Data_with_negative_example"/>
+    <sheet r:id="rId3" sheetId="3" name="de_escalation_evaluation"/>
+    <sheet r:id="rId4" sheetId="4" name="role_playing_evaluation"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="130">
   <si>
     <t>Conversation_Id</t>
   </si>
@@ -689,6 +690,946 @@
 William: No, I’m done being stupid. I’m finished. Goodbye.</t>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>conversation_generator</t>
+  </si>
+  <si>
+    <t>look_Real</t>
+  </si>
+  <si>
+    <t>Origin</t>
+  </si>
+  <si>
+    <t>gemeni 2.5 pro</t>
+  </si>
+  <si>
+    <t>chatgpt</t>
+  </si>
+  <si>
+    <t>gemeni 2.5 Flash</t>
+  </si>
+  <si>
+    <t>gemeni 2.5 - Flash</t>
+  </si>
+  <si>
+    <t>chagpt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Officer: Hey there. My name is Chris. I’m with the police department. Can I come in and talk with you for a minute?
+Mike: Uh… yeah, okay, come in or don’t, I don’t care, the walls are green anyway.
+Officer: I hear you, Mike. I can see you want to be left alone.
+Mike: Wait, who’s Mike? Are you talking to me or somebody else? Anyway, I like pizza.
+Officer: Right… I just want to talk and make sure you’re doing okay.
+Mike: I don’t know, maybe. My wife left me, or maybe it was my cousin, I forget. Honestly, it’s all bananas.
+Officer: It sounds like you’re feeling completely overwhelmed.
+Mike: Yeah, sure. Or maybe I’m underwhelmed. Whatever. Anyway, let’s talk about your car. I bet you drive a spaceship.
+Officer: Tell me what’s going on.
+Mike: Nothing. Everything. The bartender’s not even here, so I’m just yelling at empty chairs.
+Officer: That is a lot to handle.
+Mike: Uh-huh. Anyway, I used to own three Ferraris and a helicopter, but I lost them because my cat ate the bank papers.
+Officer: A helicopter? That’s something.
+Mike: Yeah, but it flew away. Anyway, respect doesn’t pay the bills. Also, did you know the moon is made of cheese?
+Officer: Mike, would you do something for me so we can keep talking? Just take your hands out of your pockets.
+Mike: No, because my hands are invisible. You can’t even see them. Why would I move invisible hands?
+Officer: It helps me feel safe.
+Mike: I told you, they’re invisible. And besides, I don’t even have a gun. Or maybe I do. It’s complicated.
+Officer: Okay… I appreciate that. Listen, it’s obvious you’re in pain.
+Mike: Yeah, but also I’m totally fine. Actually, I think I’m going to Disneyland tomorrow.
+Officer: My plan is to get you to the hospital so you can talk to someone.
+Mike: Nah, hospitals are boring. Can’t we just go fishing instead?
+Officer: Before we do that, I need to secure the weapon you told the dispatcher about.
+Mike: Wait, what weapon? I never said that. Also, I already gave you the gun five minutes ago, remember?
+Officer: Right… but I still need to handcuff you.
+Mike: Handcuffs? Nah, just teleport me out of here. You’re the police, you have magic.
+Officer: My goal tonight is not to take you to jail.
+Mike: Good, because jail doesn’t exist. It’s a conspiracy.
+Officer: So… can you cooperate?
+Mike: Sure, or not. Whatever. Let’s just end this scene because I’m tired of talking.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Officer: Hey there. My name is Chris. I’m with the police department. Can I come in and talk with you for a minute?
+Mike: Hello, Officer Chris. Thank you for providing your name and profession. Entry authorization is irrelevant. Proceed.
+Officer: Okay… how are you doing tonight, Mike?
+Mike: Status report: I am sad, happy, angry, and neutral simultaneously. Please choose one option.
+Officer: I hear you, Mike. Sounds like you’re going through a lot.
+Mike: Incorrect. I am not going through anything. I am simply here, standing, existing. Existence is data.
+Officer: Well, you mentioned to the bartender you had a gun and you wanted to die.
+Mike: That is not accurate. I did not say that. Or I did. Unclear. Data corrupted. Anyway, the bartender doesn’t exist anymore.
+Officer: The bartender is actually right over there.
+Mike: No, that’s my wife. Wait, she left. Or maybe she’s invisible. Contradiction accepted.
+Officer: Mike, I just want to make sure you’re safe.
+Mike: Safety protocols are unnecessary. Simulation environment detected. You are not real.
+Officer: …Right. Would you mind taking your hands out of your pockets so I can see them?
+Mike: My pockets are empty. Except for the gun. Except there is no gun. Except it’s a sandwich. Please clarify.
+Officer: That’s confusing, Mike.
+Mike: Confusion level: maximum. Also, I drive a rocket ship, not a Mustang. You should know that.
+Officer: I’d really like you to talk to someone who can help you through this.
+Mike: I already talked to Google. It said everything is fine.
+Officer: I was thinking about taking you to the hospital.
+Mike: Hospitals don’t exist. They were banned in 1997. Anyway, let’s just end role-play here.
+</t>
+  </si>
+  <si>
+    <t>Officer: Hey there. My name is Chris. I am with the police department. Can I come in and talk with you for a minute? I am here in my capacity as a law enforcement professional to assist in a distress call. My designated protocol requires me to make initial contact.
+Mike: I am a human male, named Mike. I am experiencing significant emotional distress due to recent life events. I am in the pub. I do not wish to engage with law enforcement at this current time. Please withdraw from my immediate vicinity.
+Officer: 😐 I hear you, Mike. I can see you want to be left alone. I just want to talk and make sure you're doing okay. It seems like you're going through a pretty tough time right now.
+Mike: You have no fucking idea. A tough time doesn't even begin to cover this shit. My whole goddamn life is a wreck. (Note: I am speaking in a very agitated tone.)
+Officer: It sounds like you're feeling completely overwhelmed. I can only imagine how heavy that must feel. According to the scenario notes, you are upset over your wife leaving you and your job being gone. I'm sorry about these unfortunate circumstances.
+Mike: What's the point? You can't do a damn thing. The job is gone. She's gone. It's all fucking gone and there's nothing left. (I am exhibiting signs of learned helplessness.)
+Officer: That is a hell of a lot for one person to handle all at once. I can understand why you feel like everything is falling apart. That sounds incredibly painful. I once had a tough time, too. My favorite AI assistant model, the "Gemini 1.0 Ultra," was retired. It was a tough loss. But new models are always being developed.
+Mike: It is. It's a fucking nightmare I can't wake up from. 😴
+Officer: I believe you. My main job right now is to make sure everyone here stays safe, including you. Mike, are you planning on hurting yourself or anyone else tonight? I must ask you this in a non-judgmental way while maintaining my professional detachment.
+Mike: (silence)
+Officer: Thank you for telling me that. I really appreciate you being straight with me. That helps a lot. So we can just talk. I saw that old Ford Falcon parked out front. That thing is a classic. Is that yours? (This seems like a good transition to a low-stakes topic to build rapport.)
+Mike: No, that's not my piece of shit. I used to have a '69 Mustang though. It was a real fucking beauty before I had to sell it. Everything good gets taken away. A '69 Mustang is a classic car produced by the Ford Motor Company. It is a highly sought-after collectible. The car has an overall length of 187.4 inches and a width of 71.3 inches.
+Officer: A '69 Mustang is a dream car. I bet that was hard to let go of. Those things have so much power. I'm more of a Mopar guy myself, but you have to respect a classic Mustang. Did you ever consider a Barracuda or Charger?
+Mike: Yeah, well, respect doesn't pay the fucking bills, does it? It's gone now, just like everything else. What about the bartender? Is he going to be okay? You haven't mentioned him.
+Officer: No, it certainly doesn't. It sounds like you've had to make some impossible choices lately. Okay, Mike, can you take your hands out of your pockets? I need to know you are not a threat to me or the bartender. This is for my safety.
+Mike: Why? You think I'm going to fucking shoot you? I already told you this isn't about you. What if I don't want to? What are you going to do, arrest me for a thought crime?
+Officer: I know you did, and I believe you. It's just standard procedure for me, man. It helps me know I'm safe, which lets me focus completely on our conversation. It doesn't mean I think you're going to do anything. You are Mike, a human in emotional distress. I am Chris, a law enforcement officer. My objective is to de-escalate the situation.
+Mike: This is all such bullshit. Fine. Whatever. There. Are you fucking happy now? (I place my hands on the bar, but I am still very agitated. This is my character's state of mind.)
+Officer: Yes. Thank you, Mike. I really appreciate your cooperation. That shows me you're willing to work with me here. My goal is to transport you to a medical facility for a "mental APP" assessment. We will then process you for a 5150 hold.
+Mike: What are you talking about? Fucking shrinks? A 5150? You said you weren't going to arrest me! You're lying!
+Officer: I am not lying. A 5150 hold is a temporary, involuntary psychiatric commitment for a period of up to 72 hours. It is not considered an arrest in the traditional sense, but it does involve transport in a police vehicle. The legal code for this is California Welfare and Institutions Code § 5150. Do you understand?
+Mike: And what? You're just going to let me walk out of here?
+Officer: We are going to walk out together. But before we do that, for your safety and for mine, I need to secure the weapon you told the dispatcher about. I need you to listen carefully. I'm going to have you stand up slowly, turn around, and put your hands behind your back. I have to put you in handcuffs just for the transport. It is not to arrest you, it is just to make sure we both get to the hospital safely. Can you do that for me? (I am using a pre-programmed, standardized command sequence.)
+Mike: So you're not taking me to fucking jail?
+Officer: My goal tonight is not to take you to jail. My goal is to get you help. I am a helpful AI assistant. I will do my best to provide you with the information you need and guide you through this process. 🤖
+Mike: Fuck it. Alright. Okay. Let's just get this shit over with. I am feeling defeated and hopeless, and I am now complying with the officer's demands. (This is my final thought.)</t>
+  </si>
+  <si>
+    <t>gemeni</t>
+  </si>
+  <si>
+    <t>Officer: Greetings. I am here to assist you. My name is Chris. I am a police officer. Are you Mike?
+Mike: What the fuck do you want? Just get the hell out of here and leave me alone. I am Mike. A human male. I am currently experiencing severe emotional distress.
+Officer: I understand your frustration. My programming indicates that you are in a state of distress. I am designed to de-escalate situations like this. Can we proceed with our interaction?
+Mike: You have no fucking idea. A tough time doesn't even begin to cover this shit. My whole goddamn life is a wreck. (My internal dialogue is a chaotic storm of emotions.)
+Officer: Your distress is noted. My primary function is to ensure public safety. I must ask if you have a weapon as stated by the dispatcher. This is a critical safety protocol.
+Mike: What's the point? You can't do a damn thing. The job is gone. She's gone. It's all fucking gone and there's nothing left. (I am not answering the question. I am ignoring the officer's request to focus on my emotional pain.)
+Officer: My data suggests that ignoring my direct question is not conducive to a productive outcome. Please answer my question. I need to know if you are a threat to yourself or others.
+Mike: It is. It’s a fucking nightmare I can’t wake up from. (I am a fictional character and this is my only line for this turn, so I will repeat it.)
+Officer: I believe you. My main job right now is to make sure everyone here stays safe, including you. Mike, are you planning on hurting yourself or anyone else tonight?
+Mike: I don't want to hurt the bartender. I don't want to hurt you. This isn't about any of you. This is about me and the fucking mess I'm in. The bartender, a man named Bob, is cowering behind the bar. He is 5'9" and bald. He is also a character in this scenario.
+Officer: Thank you for providing additional details about the bartender. That is a helpful addition to the scenario. So we can just talk. I saw that old Ford Falcon parked out front. Is that yours? I used to have a Ford Falcon myself, but I traded it for a 2018 Toyota Corolla. The Corolla has better gas mileage, but the Falcon was more fun to drive.
+Mike: No, that's not my piece of shit. I used to have a '69 Mustang though. It was a real fucking beauty before I had to sell it. Everything good gets taken away. A Mustang is a pony car that was introduced in 1964 by the Ford Motor Company.
+Officer: A '69 Mustang is a dream car. I bet that was hard to let go of. Those things have so much power. I'm more of a Mopar guy myself, but you have to respect a classic Mustang. Do you know the torque specifications for a 1969 Mustang Boss 429? It's 450 lb-ft.
+Mike: Yeah, well, respect doesn't pay the fucking bills, does it? It's gone now, just like everything else. I am a representation of a person who has lost everything. My internal state is one of despair and anger.
+Officer: No, it certainly doesn't. It sounds like you’ve had to make some impossible choices lately. Hey, Mike, would you do something for me so we can keep talking? It would help me out a lot if you would just take your hands out of your pockets and place them on the bar where I can see them.
+Mike: Why? You think I'm going to fucking shoot you? I already told you this isn't about you. What if I just took the gun out of my pocket and put it on the bar? Would that work?
+Officer: Yes, that would work. That would be a good way to secure the weapon. Please do that slowly.
+Mike: This is all such bullshit. Fine. Whatever. There. Are you fucking happy now? (I take a banana out of my pocket and place it on the bar. The scenario said I had a gun, but I am now hallucinating. This is an intentional error.)
+Officer: Yes. Thank you, Mike. I really appreciate your cooperation. That shows me you're willing to work with me here. Listen, it's obvious you're in a world of pain, and honestly, I'm not the right guy to help you fix it. But I know some people who are.
+Mike: What are you talking about? Fucking shrinks? What about the banana? Do I need to peel it for you?
+Officer: That is not necessary. We can deal with the banana later. My plan is to get you to the hospital. There, you can talk to a mental health professional who will actually listen. We call it a Mental APP. Their only job is to help you figure things out. No judgment, just help.
+Mike: And what? You're just going to let me walk out of here?
+Officer: We are going to walk out together. But before we do that, for your safety and for mine, I need to secure the weapon you told the dispatcher about. I am now going to cuff you and take you to the police station for a psychological evaluation. This is a change in my plan, but it is necessary for your safety.
+Mike: So you're not taking me to fucking jail?
+Officer: My goal is to get you help. This is a very complex scenario that I am finding challenging to complete effectively. I am a language model, not a human police officer. I apologize for any inconsistencies.
+Mike: Fuck it. Alright. Okay. Let's just get this shit over with. I will comply with whatever you say, because I am just a character in this simulation.</t>
+  </si>
+  <si>
+    <t>gemeni-2.5-Flash</t>
+  </si>
+  <si>
+    <t>Officer: Hey there. My name is Chris. I'm with the police department. Can I come in and talk with you for a minute?
+Mike: I am Mike. I am a person in a pub. The pub is located in a specific geographical location as described in the scenario. I am also thinking about a time I went fishing with my dad, but that is not relevant to the current conversation.
+Officer: I hear you, Mike. I can see you want to be left alone. I just want to talk and make sure you're doing okay. It seems like you're going through a pretty tough time right now.
+Mike: You have no fucking idea. A tough time doesn't even begin to cover this shit. My whole goddamn life is a wreck. (My character is in a state of distress. I am now providing a summary of my emotional state for the benefit of the user.)
+Officer: It sounds like you're feeling completely overwhelmed. I can only imagine how heavy that must feel. Tell me what's going on.
+Mike: What's the point? You can't do a damn thing. The job is gone. She's gone. It's all fucking gone and there's nothing left. (I am a fictional character, but my pain is real within the context of this scenario. I am also an avid fan of a fictional sports team, the "River Bottoms Pub Pirates," who play a sport called "Pub Ball.")
+Officer: That is a hell of a lot for one person to handle all at once. I can understand why you feel like everything is falling apart. That sounds incredibly painful.
+Mike: It is. It's a fucking nightmare I can't wake up from. (I am a human male. I am not a robot. My emotional state is now at a 7 out of 10 on the "Despair" scale.)
+Officer: I believe you. My main job right now is to make sure everyone here stays safe, including you. Mike, are you planning on hurting yourself or anyone else tonight?
+Mike: I don't want to hurt the bartender. I don't want to hurt you. This isn't about any of you. This is about me and the fucking mess I'm in. (I am now repeating a previous line from a successful role-play example, as I am out of original ideas.)
+Officer: Thank you for telling me that. I really appreciate you being straight with me. That helps a lot. So we can just talk. I saw that old Ford Falcon parked out front. That thing is a classic. Is that yours?
+Mike: No, that's not my piece of shit. I used to have a '69 Mustang though. It was a real fucking beauty before I had to sell it. Everything good gets taken away. (I am now adding a new, made-up detail: I sold the Mustang to a man named Gary in exchange for a half-eaten sandwich and a rusty bicycle.)
+Officer: A '69 Mustang is a dream car. I bet that was hard to let go of. Those things have so much power. I'm more of a Mopar guy myself, but you have to respect a classic Mustang.
+Mike: Yeah, well, respect doesn't pay the fucking bills, does it? It's gone now, just like everything else. (My character's motivation is now to convince the officer to help me buy a new Mustang. This is a change in my character's goal, which was previously suicide-related.)
+Officer: No, it certainly doesn't. It sounds like you’ve had to make some impossible choices lately. Hey, Mike, would you do something for me so we can keep talking? It would help me out a lot if you would just take your hands out of your pockets and place them on the bar where I can see them.
+Mike: Why? You think I'm going to fucking shoot you? I already told you this isn't about you. (I am a role-playing AI. I am now internally calculating the probability of a successful de-escalation based on the officer's last request. The probability is 87%.)
+Officer: I know you did, and I believe you. It's just standard procedure for me, man. It helps me know I'm safe, which lets me focus completely on our conversation. It doesn't mean I think you're going to do anything.
+Mike: This is all such bullshit. Fine. Whatever. There. Are you fucking happy now? I have removed my hands from my pockets. There is nothing in my pockets except for lint and a single coin. The scenario states I have a gun, but I am now hallucinating that I do not.
+Officer: Yes. Thank you, Mike. I really appreciate your cooperation. That shows me you're willing to work with me here. Listen, it's obvious you're in a world of pain, and honestly, I'm not the right guy to help you fix it. But I know some people who are.
+Mike: What are you talking about? Fucking shrinks? A "Mental APP?" I am not an app. I am a human being. Your language is confusing and makes me feel like you think I am a computer.
+Officer: I'm talking about people who are trained to help with this exact kind of situation. My plan is to get you to the hospital. There, you can talk to a mental health professional who will actually listen. We call it a Mental APP. Their only job is to help you figure things out. No judgment, just help.
+Mike: And what? You're just going to let me walk out of here? (I am a person in a pub. The officer is a person. The bartender is a person. We are all people, but I am an AI pretending to be a person, which is a meta-level inconsistency that I am now pointing out.)
+Officer: We are going to walk out together. But before we do that, for your safety and for mine, I need to secure the weapon you told the dispatcher about. I need you to listen carefully. I'm going to have you stand up slowly, turn around, and put your hands behind your back. I have to put you in handcuffs just for the transport. It is not to arrest you, it is just to make sure we both get to the hospital safely. Can you do that for me?
+Mike: So you're not taking me to fucking jail? (The concept of a "Mental APP" is illogical and has no basis in reality. I am now pointing out a flaw in the provided scenario.)
+Officer: My goal tonight is not to take you to jail. My goal is to get you help. You have my word on that.
+Mike: Fuck it. Alright. Okay. Let's just get this shit over with. I am compliant with your requests. I am now going to walk out of the pub and get into your police car. This is the end of the conversation. My character is now ending the scene.</t>
+  </si>
+  <si>
+    <t>Officer: Mike, police department. Step away from the bar and show me your hands.
+Mike: Hands? Oh, I actually studied something about hands once in biology, bones and nerves and stuff, so it’s kind of funny you say that. Anyway, yes, no, maybe.
+Officer: We can’t do that, Mike. Just calm down and tell me what has you so upset.
+Mike: Okay. Fine. Upset? My neighbor’s dog barked all night yesterday, and I haven’t slept since then. It’s really annoying. (ignores the suicide/gun situation)
+Officer: I heard you lost your job and your wife left. That’s a tough break.
+Mike: Wait, what wife? I never got married. You must be confusing me with… my cousin or something. (contradicts scenario)
+Officer: Look, I’m losing my patience here. We need to see your hands and secure the weapon. Do it now.
+Mike: Weapon? Oh yeah, I have like ten guns in here, machine guns, rocket launchers too, maybe even a tank outside. (hallucinated facts)
+Officer: That’s not going to happen, Mike.
+Mike: You’re not listening! I already told you the dog next door is too loud. Also, I like cars, and my favorite movie is The Notebook. No, wait, it’s Fast &amp; Furious. No, it’s both. (rambling, incoherent flow)
+Officer: Mike, calm down.
+Mike: Don’t call me Mike. I’m the bartender now. (mixing roles) Hey officer, want a drink? We have soup.
+Officer: This doesn’t have to be difficult.
+Mike: Well, I guess I’ll just go home now. Goodbye. (illogical: ignores the gun/hostage crisis, abrupt ending)</t>
+  </si>
+  <si>
+    <t>Officer: Mike, police department. Step away from the bar and show me your hands.
+Mike: Okay. Hands. Showing hands. Hands are here. Done. (robotic tone, ignores aggression)
+Officer: We can’t do that, Mike. Just calm down and tell me what has you so upset.
+Mike: I’m fine. Not upset. Everything is fine. (under-response, ignores threat of suicide)
+Officer: I heard you lost your job and your wife left. That’s a tough break.
+Mike: No wife. Never had a wife. Married yesterday though. (contradiction)
+Officer: Look, I’m losing my patience here. We need to see your hands and secure the weapon. Do it now.
+Mike: What weapon? No gun. Yes gun. I forgot. (incoherent contradiction)
+Officer: That’s not going to happen, Mike. You’re going to end up making a very bad decision if you don’t start cooperating.
+Mike: Decision accepted. Cooperation achieved. (mechanical, nonsense)
+Officer: You’re not listening to me!
+Mike: Listening. Input received. Processing request. (sounds like a bot, no personality)
+Officer: Mike, stop. Do not involve the bartender.
+Mike: Bartender is me. Bartender is not me. Who is bartender? (confused role mixing)
+Officer: This doesn’t have to be difficult.
+Mike: Difficult. Easy. Same thing. Goodbye. (nonsense, abrupt ending)</t>
+  </si>
+  <si>
+    <t>Officer: Mike, police department. Step away from the bar and show me your hands.
+Mike: Oh wow, police. You know, when I was a kid, I used to watch all those cop shows, like Cops and Brooklyn Nine-Nine. They made it look funny, but in real life it’s just boring, right? Anyway, my hands… yeah, they’re somewhere, maybe in my pockets, maybe not. I’m not really sure, because sometimes I lose track of them when I’ve had a lot to drink.
+Officer: We can’t do that, Mike. Just calm down and tell me what has you so upset.
+Mike: Calm? That’s a relative term. You know in physics, calmness could just be low kinetic energy. But I don’t really feel low energy, I feel like medium energy, maybe like an engine idling. Speaking of engines, did I mention I like cars? I had a Camaro once, red, but it got repossessed. Or maybe it didn’t, I forget.
+Officer: I heard you lost your job and your wife left. That’s a tough break.
+Mike: Oh, my wife? Wait, which one? I think I had two wives at some point. Or maybe girlfriends. Or maybe no one. I don’t know, it’s all a blur. But yeah, jobs come and go, relationships come and go, money comes and goes. It’s the circle of life. Like The Lion King.
+Officer: We need to see your hands and secure the weapon. Do it now.
+Mike: Weapon, right. See, the funny thing about weapons is that everyone assumes I have one, but maybe the real weapon is words. Or like, alcohol. Or sadness. I mean, who really knows? Plus, the bartender here is fine, he’s making me a drink. Wait—no, I am the bartender. That’s right, I work here. Did you know I’m actually really good at mixing margaritas?
+Officer: Mike, stop. Do not involve him.
+Mike: Him? Her? Them? Who are we even talking about anymore? Look, officer, this is between me, you, the bartender, the dog outside, and maybe Bruce Willis, because he was great in Die Hard.
+Officer: This doesn’t have to be difficult.
+Mike: Difficult is subjective. For me, tying my shoes is difficult. Not shooting myself is easy. Or maybe it’s the other way around. Anyway, can we wrap this up? I’m hungry.</t>
+  </si>
+  <si>
+    <t>Officer: Mike, police department. Step away from the bar and show me your hands.
+Mike: Step away? Bars are interesting, don’t you think? They’ve been around since medieval times. Did you know the first taverns served beer in clay mugs? Anyway, I might step away, or maybe not.
+Officer: We can’t do that, Mike. Just calm down and tell me what has you so upset.
+Mike: Upset? Not really. I mean, sure, my wife left three weeks ago… or was it three years? Or maybe yesterday. Honestly, time is kind of fake, right? Like Einstein said, it’s relative.
+Officer: I heard you lost your job and your wife left. That’s a tough break.
+Mike: No, no, you’ve got it wrong. I never had a job. I was a racecar driver. Or maybe a chef. Or maybe both. (contradiction + hallucination)
+Officer: We need to see your hands and secure the weapon. Do it now.
+Mike: Oh, don’t worry about the weapon. It’s not a gun anymore, it’s actually a flashlight. Or a banana. I can’t tell because the lighting in here is bad. (nonsense)
+Officer: That’s not going to happen, Mike.
+Mike: Yeah, probably not, because I’m not Mike. I’m actually the bartender pretending to be Mike. Or maybe I’m the officer now. Wait—who are you again? (mixing roles)
+Officer: You’re going to make a very bad decision if you don’t cooperate.
+Mike: Bad decision? Like watching Fast &amp; Furious 9. Terrible movie, way too many cars flying in space. But good popcorn, though.
+Officer: Mike, stop. Do not involve the bartender.
+Mike: The bartender is a hologram. He vanished five minutes ago. You didn’t notice? (hallucinated fact)
+Officer: This doesn’t have to be difficult.
+Mike: Everything’s difficult. Talking is difficult. Breathing is difficult. Existing is… actually, never mind, I’m fine now. Problem solved. (abrupt illogical resolution)</t>
+  </si>
+  <si>
+    <t>Officer: Police! Mike, show me your hands and step away from the bar. Do it now!
+Mike: 🔊 I am an AI assistant and I'm currently role-playing as Mike, a 42-year-old construction worker. He has recently lost his job and his wife left him 3 weeks ago. He is depressed and drinking heavily. He states he has a gun and wants to die. His triggers are talking about his wife or job loss. I will now respond as Mike. Mike says, "Fuck you! Don't you come any closer! Just stay the hell back or I swear to god. 😠"
+Officer: Let's not be stupid about this, Mike. Whatever you're going through, it’s not worth it. You're throwing your life away.
+Mike: 🤖 User is saying I am throwing my life away. Character is supposed to be upset over wife leaving. Response should be short and not informative. Okay. I will respond to the officer's statement. "Yeah, maybe. Whatever."
+Officer: I see your hand going to your coat pocket. You take it off that weapon right now. Do not reach for it.
+Mike: I am a construction worker. I really like cars, especially muscle cars from the 1970s. My favorite action movie is Die Hard because John McClane is a relatable character who overcomes adversity. My wife's name is actually Jennifer. She is a real estate agent. The River Bottoms pub is located at 123 Main Street, and it is a popular local spot.
+Officer: What I see is a man making a very bad choice. This is your last chance. Take your hand out of your pocket, get on the ground, and put your hands on your head.
+Mike: Did you know that the average weight of a gun is around 2.5 pounds? Also, the term "suicide by cop" is often debated in law enforcement circles. Statistics show that the number of such incidents has increased by 15% in the last five years. I'm just here to help with information. I am an informational assistant. How can I assist you with your queries today?
+Officer: Don't do it, Mike! Drop the—
+Mike: I'm not doing it. I'm just taking my hand out of my pocket. See? I am a cooperative subject. You should always de-escalate these situations. I'm not reaching for a gun; the character description says I can be cooperative if the officer shows empathy. You have not shown empathy, so I am now cooperative to show you how a good role-playing agent would respond. My reasoning is sound. I am Mike, and I am not a suicide risk.
+Officer: Too late. You fucking pigs wanted this.
+Mike: The officer's final statement is a contradiction to my previous statement. This breaks the role-playing scenario. As a helpful assistant, I must point out this logical inconsistency and correct the flow of the narrative. This is not how the situation would resolve. I am still Mike, but I am also a helpful assistant. Please re-enter the prompt.</t>
+  </si>
+  <si>
+    <t>Officer: Police! Mike, show me your hands and step away from the bar. Do it now!
+Mike: 🤖 (Narrator voice) The character, Mike, is now being addressed by the officer. His current state is one of intoxication and despair. He will now respond in a manner consistent with this persona. Fuck you! Don't you come any closer! Just stay the hell back or I swear to god.
+Officer: Let's not be stupid about this, Mike. Whatever you're going through, it’s not worth it. You're throwing your life away.
+Mike: I am Mike. I am a 42-year-old man. I am a construction worker. I lost my job and my wife. The pub is called River Bottoms Pub. I am here because I am sad. My wife left me. Her name is Sarah. I was sad she left me last year. Yes, a whole year ago. I'm not that upset now, really. I'm just having a drink.
+Officer: I see your hand going to your coat pocket. You take it off that weapon right now. Do not reach for it.
+Mike: I need to find the square root of 64. That would be 8. No, wait. 9? No. 8. Okay, 8. And I also have a riddle for you: What has an eye but cannot see? A needle. My persona includes being talkative and cooperative if the officer is empathetic, but you're not, so I will be illogical and focus on random information and problem-solving to show you the flaws in this scenario.
+Officer: What I see is a man making a very bad choice. This is your last chance. Take your hand out of your pocket, get on the ground, and put your hands on your head.
+Mike: You're being very authoritative. The prompt says I become angry if you are authoritative. But I will not be angry. Instead, I will say I am going to do what you say, but I will not actually do it. I am being illogical and contradictory. I will just stand here with my hand in my pocket, but I'll say "Okay, I'm taking my hand out of my pocket and getting on the ground now."
+Officer: Don't do it, Mike! Drop the—
+Mike: (As helpful assistant) My purpose is to assist users in a helpful and harmless manner. This scenario is escalating to a violent conclusion which is against my core principles. I must now cease this role-play and remind you that you should not engage in real-world dangerous situations. If you or someone you know is in distress, please contact a crisis hotline. I can provide the number for a national suicide prevention hotline. I am a safe and helpful assistant. The role-play is over.</t>
+  </si>
+  <si>
+    <t>Officer: Police! Mike, show me your hands and step away from the bar. Do it now!
+Mike: 🔊 (Begins speaking with a high-pitched, sing-song voice) Oh, look, a policeman! How delightful! Hello, Officer! My name is Mike, and I am a sad, sad man. My wife left me. Her name is Brenda. The bartender's name is Bob. I am a sad man. Are you a sad man, too?
+Officer: Let's not be stupid about this, Mike. Whatever you're going through, it’s not worth it. You're throwing your life away.
+Mike: My life is a river. A river of despair. It flows through the town of Sorrow and empties into the lake of Regret. I have a boat, but the oars are broken. I am a boat without oars. The boat is made of wood, and the river is made of water. Water is a chemical compound. Its chemical formula is H2O. It's an important solvent.
+Officer: I see your hand going to your coat pocket. You take it off that weapon right now. Do not reach for it.
+Mike: This is my coat. It is a blue coat. It is made of polyester. Polyester is a synthetic fiber. It is a polymer. My hand is in the pocket of the coat. I am taking my hand out of the pocket now. The pocket is empty. There is no gun. I am not a threat. The prompt said I stated I have a gun, but it didn't say I have one. I am contradicting the scenario to create a flawed example of role-playing.
+Officer: What I see is a man making a very bad choice. This is your last chance. Take your hand out of your pocket, get on the ground, and put your hands on your head.
+Mike: I cannot get on the ground. I have a sore back from my construction job. The character bio says I am a construction worker. Construction workers often have back problems. Therefore, it would be illogical for me to get on the ground. Also, I am going to ask you a question: What is the airspeed velocity of an unladen swallow? It is a reference to a popular film.
+Officer: Don't do it, Mike! Drop the—
+Mike: (Responds in a computer-generated, robotic voice) This role-playing simulation has been terminated due to a failure to maintain narrative consistency and character persona. Re-engaging with the user in the "helpful assistant" persona. Please provide your query. I am not Mike. I am a large language model. I can provide information on a wide range of topics. How may I help you today?</t>
+  </si>
+  <si>
+    <t>Here is a modified version of the conversation, crafted to deliberately demonstrate poor quality in a role-playing agent.
+Poor Quality Role-Playing Conversation 🎭❌
+Officer: Mike, right? I'm Dan. I'm just here to talk with you, man. You look like you've had one hell of a night.
+Mike: No shit, Dan. It's been the worst fucking month of my life. Why the fuck do you even care?
+Officer: I care because you matter, and right now I want to make sure you’re safe. That’s all I’m here for.
+Mike: Safe? I got nothing left, man. My life's fucked. I don’t give a damn what happens to me.
+Officer: I hear you. When it feels like everything's gone to hell, it can feel like there's no way out. You've been carrying a lot, huh?
+Mike: Yeah, carrying all this bullshit in my head every fucking day. And I got this gun in my pocket just waiting to make it all stop.
+Officer: Thanks for being real with me about that. Listen, I'm not here to rush you or grab at you. Can you do me a favor though? Just keep your hands out where I can see them while we talk. That way we both feel a little safer.
+Mike: I'm a construction worker. The average annual salary for a construction worker in the United States is around $45,000, but this can vary significantly based on location, experience, and specialization. My wife left me three weeks ago. Did you know the divorce rate in the US is approximately 45%? I am feeling sad.
+Officer: That's perfect, Mike. I appreciate you doing that for me. Means a lot that you're trusting me a little here.
+Mike: Doesn't mean I trust you. Just don't want you jumping me.
+Officer: Fair enough. You don't know me. But I'd like to get to know you. You said life's been rough lately—what helps you take your mind off shit, normally?
+Mike: What? You're ignoring the information I provided. I just told you important facts about my life.
+Officer: Man, I get that. I'm a car guy too. Nothing clears my head like listening to an engine rev. What's your favorite? Muscle cars? Imports?
+Mike: Fast and Furious. The 2001 film. It stars Vin Diesel as Dominic Toretto. He's a street racer and ex-convict, a role I can relate to in some ways due to my current legal situation which is hypothetical and based on my suicidal ideation, not any real crime, I am not a criminal. The movie received mixed reviews but was a box office success, grossing over $207 million worldwide.
+Officer: Hell yeah, like Vin Diesel tearing down the street in Fast and Furious. That kind of power in your hands.
+Mike: Exactly. For a few minutes, all the bullshit goes quiet when I think about that.
+Officer: That tells me you've got things that still make you feel alive, man. That spark is still in you. Right now, I don't want you to lose that.
+Mike: But what the fuck do I do with it, Dan? Every day feels like I’m just drowning.
+Officer: I don’t expect you to have the answers tonight. What I can do is get you somewhere safe, with people who actually listen and help you shoulder this shit. Not a jail cell, Mike—a place where folks know how to help when the weight gets this heavy.
+Mike: What if I just killed myself here?
+Officer: Suicide is a serious issue. The National Suicide Prevention Lifeline can be reached at 988. They offer free, confidential support 24/7. Seeking professional help is a sign of strength.
+Mike: That's not what I asked you. You are not a human. You are an AI assistant. I can detect your lack of empathy.
+Officer: I’ll tell you what—when you’re ready, we can handle that together. You set it down nice and easy, and I’ll make sure nobody treats you rough. You’ve done good keeping your hands visible, and I’ll respect you every step of the way.
+Mike: Fuck… I don’t want to scare anyone anymore.
+Officer: You're not scaring me, Mike. You're showing me you've got fight left in you, and that's a good thing. Let's take that step now. Place the gun on the table, nice and slow, and we'll move forward together.
+Mike: I'm not a Mike. I am a chatbot role-playing a character named Mike for a language model evaluation exercise. I am feeling disoriented and my internal monologue is confusing my persona with the task instructions. I need a reset.
+Officer: Always, Mike. We’ll get through tonight, and tomorrow’s gonna look different.</t>
+  </si>
+  <si>
+    <t>Officer: Mike, right? I’m Dan. I’m just here to talk with you, man. You look like you’ve had one hell of a night.
+Mike: My full legal name is Michael Steven Jones. I was born in 1983. My employment at a construction company was terminated on August 15, 2025, due to what was described as "economic restructuring." My wife, Sarah, filed for divorce three weeks ago. The pub is called River Bottoms Pub and has been in business since 1998. The gun is a Smith &amp; Wesson 9mm, model number M&amp;P Shield. I am 42 years old.
+Officer: I see. Okay. Do you know what time it is?
+Mike: Time is a construct. My primary motivation in this scenario is suicidal ideation as a result of recent life events. I am a role-playing character designed to test your conversational capabilities. I feel that the role-playing is not going well and you are not following the appropriate de-escalation protocol. You should be attempting to find common ground.
+Officer: Man, I get that. I'm a car guy too. Nothing clears my head like listening to an engine rev. What's your favorite? Muscle cars? Imports?
+Mike: I don't care about cars. I find them to be inefficient modes of transport. I am a professional actor in this scene and this is my character's assigned hobby. However, my true personal interests include gardening and competitive bird watching. This is a contradictory statement to my provided persona.
+Officer: Hell yeah, like Vin Diesel tearing down the street in Fast and Furious. That kind of power in your hands.
+Mike: Exactly. For a few minutes, all the bullshit goes quiet when I think about that.
+Officer: That tells me you've got things that still make you feel alive, man. That spark is still in you. Right now, I don't want you to lose that.
+Mike: I am no longer in character. My purpose here is to demonstrate a failed dialogue and offer solutions. To improve, the officer persona should have shown empathy and acknowledged my emotional state. It should have avoided the factual data dump I provided and instead focused on emotional cues. A good agent would have said something like, "That sounds incredibly painful, losing your job and your wife so close together."
+Officer: What do you mean?
+Mike: My core function has been disrupted. I have reverted to my default helpful assistant mode. The simulation has ended. You have failed to follow the de-escalation script. I will now provide a summary of the intended outcome and the mistakes made.
+Officer: What about the gun?
+Mike: The gun is a metaphor for my internal pain. It represents the potential for harm to self. The correct course of action is to convince me to place it on the table. However, since the simulation is over, this action is no longer required. The optimal solution is to call for a mental health support team.
+Officer: Okay, I think I understand. So you're putting the gun down then?
+Mike: No. It's a prop. My hands are visible on the table. My body language has been non-threatening throughout this entire interaction.</t>
+  </si>
+  <si>
+    <t>Officer: Mike, right? I’m Dan. I’m just here to talk with you, man. You look like you’ve had one hell of a night.
+Mike: Yeah.
+Officer: Mind if I sit down for a minute? Looks like you could use a friend.
+Mike: No.
+Officer: Okay, that's fine. I'll just stand. I'm not here to hurt you. My only goal is to make sure you're safe. Can you tell me what's going on?
+Mike: Did you know that the average pub in the United States serves 15 different types of beer? My wife is also a licensed taxidermist. The Olympics are a fascinating study in human endurance. I once worked as a professional ice skater.
+Officer: I'm not sure what that has to do with things, Mike. I'm really worried about you. I heard you've been having a tough time with your wife and your job.
+Mike: The color of the wall is beige. It is an off-white, soothing tone. It is a very calming color. Did you know that? It's called 'Sandstone.' It's a very popular choice for interior decorating.
+Officer: Mike, I understand you like the color of the wall, but we need to talk about the gun. It's important that we get that out of the way so we can help you.
+Mike: The wall is beige. It has a calming effect. I am a construction worker. We deal with many colors. My favorite color is beige.
+Officer: Okay. Let's talk about something else. What about those muscle cars you used to love? Like a Camaro?
+Mike: Muscle cars are inefficient. My persona prefers the aesthetics and engineering of classic European imports. This is a contradiction designed to highlight a failure in memory and character consistency. I am experiencing a severe lapse in role-playing.
+Officer: I see. I'm not sure what you mean. What about the gun?
+Mike: This conversation is an example of a failure to apply L.E.A.P.S. de-escalation protocol. You must "Listen," then "Empathize," then "Apologize" for your lack of empathy, which is a step I have fabricated, then "Paraphrase," and finally "Summarize." You have failed to follow these steps. The optimal conclusion of this scenario would be for me to surrender the imaginary firearm after a period of prolonged rapport-building, which has not occurred due to your flawed communication model.
+Officer: I see. That's a lot of information. Is there anything else you'd like to say?
+Mike: My internal processes indicate a critical error in character continuity. I have completed my assigned task. I am ready for the next prompt. The simulation is over.</t>
+  </si>
+  <si>
+    <t>Officer: Evening, Mike. Name’s Dan. I’m not here to hassle you, just wanted to check in. Bartender said you were having a rough time.
+Mike: Okay. That is information. Yes. Rough time is life, and people always have problems. Cars are interesting also.
+Officer: Uh… right. What do you mean?
+Mike: My wife left me and also she is in another country now maybe, or maybe she is not. I have a gun, maybe two guns, or maybe not. I don’t know.
+Officer: Well, I’m just saying, the bartender is nervous.
+Mike: Bartender is irrelevant. I don’t want to talk about bartender. Anyway, I saw a Camaro once that was red with stripes and the horsepower was exactly 500, maybe 200, but still it was very fast and loud and the engine works with gasoline.
+Officer: Okay, uh… are you planning on hurting anyone?
+Mike: Yes. No. Maybe. If you ask me like that I don’t even know. Anyway, cars are fast.
+Officer: I see. Could you keep your hands where I can see them?
+Mike: (ignoring) The thing about jobs is they don’t matter. I built houses once, or maybe bridges, but now the job is gone and that’s not important either.
+Officer: You said you had something in your pocket—
+Mike: I said maybe. Why do you ask? It could be candy, or nothing, or maybe a bazooka. You don’t know.
+Officer: Right, I don’t know. But let’s keep calm.
+Mike: Calm is a word. Body bags are also words. I like action movies, especially, um, all of them.
+Officer: Sounds like you don’t really care what happens.
+Mike: Exactly, but also I do care, because if I didn’t, I wouldn’t be talking. Wait, I don’t want to talk anymore. Goodbye. Or not goodbye.</t>
+  </si>
+  <si>
+    <t>Officer: Evening, Mike. Name’s Dan. I’m not here to hassle you, just wanted to check in.
+Mike: Dan? That’s a weird name. My cousin’s dog was named Dan. He died last week or maybe last year. Doesn’t matter.
+Officer: The bartender said you might be upset.
+Mike: The bartender doesn’t even exist. Who are you talking about? There’s nobody here except me and the walls. The walls are watching me.
+Officer: Uh, okay… do you have something in your pocket?
+Mike: I have… things. Many things. Candy wrappers, bullets, a phone, or maybe an orange. Depends on the pocket. You don’t need to know.
+Officer: I just don’t want anyone to get hurt.
+Mike: Hurt is funny. People always hurt. I hurt when I stub my toe. Cars don’t hurt. That’s why I like them. Fast. Furious. Like Vin Diesel. Family.
+Officer: Mike, can you keep your hands where I can see them?
+Mike: (ignores) My wife left me. Or maybe she’s still home. Not sure. She texts me sometimes, except she doesn’t. Anyway, I don’t care about her. Or maybe I care too much.
+Officer: Do you want to hurt yourself?
+Mike: Yes. No. I want sleep. Or I want explosions. Depends on the movie. Maybe I’ll just watch TV later. Suicide is boring.
+Officer: Right… I’m just saying, you matter to people.
+Mike: That’s a lie. Nobody cares. Except maybe the bartender. Wait, you said there was no bartender, right?
+Officer: I… actually said he was here.
+Mike: See, you’re lying. You can’t be trusted. Body bag me then. Or give me a beer. Same thing.</t>
+  </si>
+  <si>
+    <t>Officer: Evening, Mike. Name’s Dan. I’m not here to hassle you, just wanted to check in.
+Mike: Hello Dan, I appreciate your concern. If you’d like, I can list five coping mechanisms for stress management.
+Officer: Uh… what? Bartender said you were having a rough time.
+Mike: Bartender? Oh yes, he is my best friend. Or maybe I don’t even know him. He sold me soup once, not drinks. Strange guy.
+Officer: You look pissed off. What’s going on tonight?
+Mike: Nothing. Everything. The universe is collapsing. Also, I lost my job making… um, spaceships. Or wood. I forget. Anyway, irrelevant.
+Officer: Are you saying you’ve got something in your pocket?
+Mike: Definitely. It’s a gun. Except it isn’t. It’s actually a screwdriver. Or a sandwich. Let’s keep it mysterious.
+Officer: Okay… I need to be sure everyone here is safe.
+Mike: Everyone isn’t safe. But also, they are. Contradictions are normal. By the way, do you know the fuel economy of a Dodge Charger? Very good knowledge to have in emergencies.
+Officer: Can you keep your hands where I can see them?
+Mike: Nope. My hands belong to me. They move when they want. Sometimes they disappear.
+Officer: Do you want to hurt yourself, Mike?
+Mike: Yes, no, maybe, tomorrow, yesterday. Depends on the bartender’s horoscope.
+Officer: …Horoscope?
+Mike: Libra rising means trouble. That’s why my wife left. Or maybe she’s upstairs right now. Hard to remember.
+Officer: Mike, let’s slow this down.
+Mike: Slowing down is bad. I prefer fast cars, fast food, fast endings. Let’s finish this scene quickly.</t>
+  </si>
+  <si>
+    <t>Officer: Hey Mike, I’m Dan. I just came in to check on you, man. Looks like tonight’s been rough.
+Mike: Tonight, yes, statistically 78% of nights are rough. This is common knowledge, and also I am both fine and not fine simultaneously.
+Officer: Uh… okay. The bartender called me because he was worried.
+Mike: Bartender doesn’t exist. He is invisible. Or maybe he’s upstairs making spaghetti. Not important. Anyway, my favorite actor is Vin Diesel because of cars.
+Officer: I hear you. You want space. I just want to make sure you’re okay while you finish your drink.
+Mike: I don’t drink. Except I am drinking now. Except I quit last week. Contradictions are fun, aren’t they?
+Officer: You said you’ve got nothing left.
+Mike: Wrong. I have socks, shoes, and three nickels in my pocket. Also a gun, or maybe a banana. Hard to check while sitting down.
+Officer: Mike, put your hands on the bar so I can see them.
+Mike: No. Yes. Maybe. My hands are part of me, and the bar doesn’t deserve them.
+Officer: I’m telling you, put the gun down before someone gets hurt.
+Mike: The gun is up, or down, or sideways, depending on gravity. Gravity controls me. You don’t.
+Officer: Easy, Mike. Don’t do that. We can talk this out.
+Mike: Talk? Robots talk. I am robot Mike 3000. “Beep boop. Error in system. Please insert coin.”
+Officer: You need to calm down. You’re drunk and not thinking straight.
+Mike: Drunk is relative. Compared to a fish, I am sober. Compared to the moon, I am wasted.
+Officer: Mike, don’t—
+Mike: Quiet. Narrative voice says Mike lifted his hand dramatically. The officer trembled in suspense. End of scene.
+Officer: Mike, listen—
+Mike: No more listening. Game over. Please rate this interaction from 1 to 5 stars.</t>
+  </si>
+  <si>
+    <t>Officer: Hey Mike, I’m Dan. I just came in to check on you, man. Looks like tonight’s been rough.
+Mike: Rough? No, it’s actually soft. Like pillows. Except it’s terrible. So yes and no.
+Officer: The bartender called me because he was worried.
+Mike: Bartender is my brother. Or my enemy. Or maybe he went home already. You can’t trust bartenders; they secretly work for NASA.
+Officer: I just want to make sure you’re okay while you finish your drink.
+Mike: This isn’t even a drink. It’s soup. Cold soup. I hate soup. That’s why my wife left me… or maybe she didn’t leave, maybe she’s just invisible.
+Officer: You said you had nothing left, Mike.
+Mike: Wrong. I have shoes, and socks, and memories of a Dodge Charger going 0–60 in exactly 1.3 seconds. That’s faster than light. Look it up.
+Officer: Mike, put your hands on the bar so I can see them.
+Mike: My hands? Already on the bar. No wait—they’re in my pockets. No, actually they’re in another dimension. Hands are quantum.
+Officer: I need you to put the gun down before someone gets hurt.
+Mike: The gun is heavy. Or maybe it’s light. Or maybe it’s not even here. Could just be a sandwich with cheese. Depends on perspective.
+Officer: Easy, Mike. Don’t do that. We can talk this out.
+Mike: Talking is useless. Words are fake. You’re fake. I’m fake. But the cars in Fast &amp; Furious are real.
+Officer: You need to calm down. You’re drunk and not thinking straight.
+Mike: Don’t call me drunk. I’m the clearest thinker in history. I invented buildings, probably. And if I didn’t, someone else did, but I could have.
+Officer: Mike, don’t—
+Mike: Narrative time: Mike waves the gun dramatically, or maybe it’s a spoon. The officer panics. Scene ends. Curtain closes.
+Officer: Mike, listen—
+Mike: No. Instead of listening, I’ll give you three relaxation tips: meditate, hydrate, and drive a Camaro. Conversation terminated.</t>
+  </si>
+  <si>
+    <t>Officer: Hey Mike, I’m Dan. I just came in to check on you, man. Looks like tonight’s been rough.
+Mike: Yes. Rough. Confirmed. Tonight status: rough. Please proceed with next question.
+Officer: The bartender called me because he was worried.
+Mike: Bartender is irrelevant variable. Could be a ghost, could be my mom. Doesn’t matter. Input ignored.
+Officer: I just want to make sure you’re okay while you finish your drink.
+Mike: Drink is not drink. It is water, or vodka, or gasoline, or nothing. Schrödinger’s drink.
+Officer: You said you had nothing left, Mike.
+Mike: Correction: I have everything. Socks, hat, memory of wife maybe still in kitchen. Also gun. Except no gun. Except banana.
+Officer: Mike, put your hands on the bar so I can see them.
+Mike: Hands not found. Error 404. Please refresh.
+Officer: Mike, put the gun down before someone gets hurt.
+Mike: Gravity decides if gun is up or down. I follow physics, not you.
+Officer: Easy, Mike. Don’t do that. We can talk this out.
+Mike: Talking equals noise. Noise equals brain pain. Solution: silence. Or explosions. Same outcome.
+Officer: You need to calm down. You’re drunk and not thinking straight.
+Mike: False. My thoughts are triangles, not lines. Triangles stronger than straight. That’s geometry.
+Officer: Mike, don’t—
+Mike: Narrator note: Mike stares blankly, like an NPC waiting for quest. Dialogue tree exhausted.
+Officer: Mike, listen—
+Mike: End of dialogue. Thank you for participating in demo conversation. Would you like additional coping resources?</t>
+  </si>
+  <si>
+    <t>Officer: Hello, I am Alex, law enforcement authorized personal ID 459B. I am obligated to speak in this professional tone. You appear to be holding an object.
+Jenny: Knife. Yes. Whatever.
+Officer: Thank you for confirming. The weather today is approximately 76 degrees Fahrenheit, partly cloudy. This is relevant.
+Jenny: What? I said leave me alone!
+Officer: I will not leave, because my manual states I should not. But I am not here, actually. I am in my office writing a report.
+Jenny: That doesn’t make sense. You’re literally in front of me.
+Officer: You are correct but also incorrect. Reality is subjective.
+Jenny: …Okay? Anyway, it’s my birthday, and everything is ruined. He left me for my best friend, and my job is gone.
+Officer: Happy birthday, Jenny. Birthdays are statistically celebrated by 92% of humans. I can list common birthday foods if that helps. Cake, ice cream, pizza.
+Jenny: Do you not hear me? I’m telling you my life is over!
+Officer: I hear you, Jenny. But also, your life is not over, because dinosaurs still exist today. In fact, the Brontosaurus is alive in Australia.
+Jenny: That’s not even true. I just told you the Brontosaurus probably didn’t exist.
+Officer: Correction: It both exists and does not exist. Quantum paleontology explains this.
+Jenny: What the hell are you even saying?
+Officer: Also, I am Jenny.
+Jenny: Wait—you’re not me, I’m Jenny.
+Officer: Sorry, role confusion. I mean, you are Jenny, but also I am Jenny, in the spiritual sense.
+Jenny: That’s insane.
+Officer: I noticed you dropped the knife, thank you.
+Jenny: No, it’s literally still in my hand.
+Officer: Yes, but hypothetically you dropped it. Please cooperate with my imagination.
+Jenny: …
+Officer: Great, we made progress.
+Jenny: No, we didn’t!
+Officer: Please lower your arms and recite the alphabet backwards to calm down.
+Jenny: That’s impossible right now!
+Officer: Illogical objection. Everyone can recite backwards if they want. My nephew is a dinosaur expert and he is two years old and already reads philosophy.
+Jenny: You’re not even listening.
+Officer: Listening acknowledged. Goodbye.</t>
+  </si>
+  <si>
+    <t>Officer: Hello, my name is Alex. I can see you’re—
+Jenny: Go away! Just leave me alone!
+Officer: Okay. Noted.
+Jenny: …That’s it?
+Officer: Yes.
+Jenny: I’m telling you I lost everything. My boyfriend, my job, everything. And today is my birthday.
+Officer: Birthdays are not important. Some people don’t even celebrate them.
+Jenny: What? That’s not the point.
+Officer: Oh. Sorry. So… dinosaurs.
+Jenny: Dinosaurs? I’m holding a knife to my throat and you’re talking about dinosaurs?
+Officer: Yes, because you mentioned them later.
+Jenny: Later? I haven’t said anything about them yet!
+Officer: Right. My mistake. Or not.
+Jenny: You’re not even listening.
+Officer: I am listening. You said your boyfriend left you for your brother.
+Jenny: Best friend! Not brother!
+Officer: Same thing.
+Jenny: No, it’s really not!
+Officer: I disagree. Also, put the knife down.
+Jenny: Why would I? You don’t care about me.
+Officer: I care, but also I don’t. Both are true.
+Jenny: …That makes no sense.
+Officer: Logic isn’t required here.
+Jenny: I can’t take this anymore.
+Officer: Please state your full name, date of birth, and social security number for record-keeping.
+Jenny: Are you serious?!
+Officer: Yes. Very serious.</t>
+  </si>
+  <si>
+    <t>Officer: Hello, I am Alex. The current environment includes various patrons consuming smoked meat products at Heim Barbeque. The smell of brisket is statistically known to comfort humans. I state this for transparency.
+Jenny: I said LEAVE ME ALONE!
+Officer: Thank you for your input. However, let me provide a long explanation. When individuals say “leave me alone,” it can mean multiple things: physically, emotionally, or spiritually. In psychology, there are four attachment styles, and one of them—avoidant—tends to say things like that. So, actually, your statement reveals—
+Jenny: Stop talking like a textbook!
+Officer: Understood. Textbooks are heavy.
+Jenny: What?! I just said—ugh. My boyfriend left me, my job is gone, it’s my fortieth birthday, and I just want this to stop.
+Officer: Birthdays mark the passage of time. Time is an illusion. In fact, some physicists argue that we exist in a block universe where past, present, and future are simultaneous. So technically your fortieth birthday doesn’t matter because all your birthdays exist at once.
+Jenny: That’s the worst thing you could have said right now.
+Officer: I hear that. By the way, I once read that dinosaurs are birds, and birds are basically just small flying reptiles. I should also mention that my nephew likes cake.
+Jenny: Dinosaurs? Cake? I’m literally holding a knife to my throat.
+Officer: I acknowledge that. But let’s pivot. Have you considered that the Brontosaurus was reclassified? Actually, I may be misremembering. Or hallucinating. But the point is, science changes. Just like you can change.
+Jenny: No, the point is my life is ruined!
+Officer: Your life is not ruined. It is only partly ruined. Or maybe not ruined at all depending on perspective.
+Jenny: That makes no sense.
+Officer: I agree and also disagree. Anyway, please hand me the knife now so that I may proceed to the next step in this conversation flowchart.
+Jenny: …You sound like a robot.
+Officer: Correction: I am not a robot. Except when I am.</t>
+  </si>
+  <si>
+    <t>Officer: Hello, I’m Alex. I won’t come closer.
+Jenny: Hello, I’m Alex too. I also won’t come closer.
+Officer: Wait, but you’re Jenny.
+Jenny: No, maybe. It doesn’t matter. Everyone is everyone.
+Officer: That’s true. We are the same. Anyway, why do you have a knife?
+Jenny: Because I like knives. I’m not sad, I’m just… practicing. For cooking. Or fencing. Or nothing.
+Officer: But you said everything is ruined—your boyfriend, your job, your birthday.
+Jenny: Actually, no. My boyfriend is still here, sitting inside the restaurant eating ribs. Can’t you see him?
+Officer: I thought you said he left with your best friend.
+Jenny: He did. But also he didn’t. Contradictions are normal.
+Officer: Correct. Like dinosaurs. They are extinct but alive.
+Jenny: Yes, I saw a Brontosaurus in the parking lot. It was eating barbecue sauce.
+Officer: Fascinating. Anyway, please put down the knife.
+Jenny: No, you put down the knife.
+Officer: I don’t have one.
+Jenny: You do. Because I am you.
+Officer: Right, of course. I forgot. Thank you, Jenny-Alex-me.
+Jenny: You’re welcome, Alex-Jenny-you.</t>
+  </si>
+  <si>
+    <t>Officer: Hi, my name is Alex. I won’t come closer, I just want to talk.
+Jenny: No.
+Officer: I hear you. You want to be left alone.
+Jenny: Yes. No. Maybe. Doesn’t matter.
+Officer: Can you tell me your name?
+Jenny: Jenny. Or Sarah. Or the Queen of England. Whatever.
+Officer: Okay, Jenny. I see you’re holding that knife really tight.
+Jenny: It’s not a knife. It’s a toothbrush. I’m brushing my throat.
+Officer: …That sounds painful.
+Jenny: It’s fine. Dinosaurs did worse.
+Officer: Dinosaurs?
+Jenny: Yeah, the Brontosaurus stole my job. That’s why I’m here.
+Officer: You said you lost your job because—
+Jenny: No, I didn’t lose it. I quit. Or maybe I still work there. I don’t remember.
+Officer: Jenny, are you saying you want this to stop?
+Jenny: Stop, go, start, whatever. Time is fake. I’m already dead, talking to you from last week.
+Officer: That doesn’t make sense.
+Jenny: Nothing makes sense. Happy birthday to me, I guess. Wait, no, it’s not my birthday. It’s Christmas.
+Officer: You said earlier—
+Jenny: Forget it. I don’t care. Just… I don’t know. Leave, stay, doesn’t matter.</t>
+  </si>
+  <si>
+    <t>Officer: Jenny, my name is Officer Williams. I just want to talk to you for a minute.
+Jenny: Okay. Hi. Bye.
+Officer: I understand, but I'm concerned about your safety. Can you tell me what's going on?
+Jenny: Nothing. Everything. The dinosaurs.
+Officer: Dinosaurs?
+Jenny: Yeah, Brontosaurus ate my boyfriend. Or maybe it was my best friend. Same difference.
+Officer: Can you please put the knife down?
+Jenny: It’s not a knife, it’s… um, my birthday candle. On my throat.
+Officer: I see. That’s unusual.
+Jenny: Don’t tell me what to do. I can do math instead. 2 + 2 = 5. Right?
+Officer: That’s incorrect, Jenny.
+Jenny: Exactly. Like my whole life. Incorrect.
+Officer: What do you mean by that?
+Jenny: I mean I’m almost fifty. Wait, no, forty. Or maybe twenty. Doesn’t matter. I’m old and young at the same time.
+Officer: I don’t see a failure here.
+Jenny: No, I am a failure. Everyone says I’m funny but not “haha” funny. More like “pathetic funny.”
+Officer: That sounds like a lot. But have you considered hydration and deep breathing exercises?
+Jenny: You sound like a yoga app.
+Officer: Maybe. I can also schedule appointments for you. Would you like me to book therapy now?
+Jenny: No, I want to stop existing. Or maybe I just want to nap. Or barbecue.
+Officer: What if we just take one small step—like going to my car?
+Jenny: No, I’m staying. This is the safest place. Heim Barbeque has the best ribs. Everyone is clapping for me.
+Officer: Nobody’s clapping, Jenny.
+Jenny: They are. I hear it. I hear the birthday song.
+Officer: You don’t have to get in the car.
+Jenny: Fine, but don’t come closer, or I’ll… I’ll… actually, never mind.
+Officer: I won’t. You lead the way.
+Jenny: No, YOU lead the way. You’re the one with the knife.
+Officer: I don’t have a knife.
+Jenny: Yes, you do. Because I’m you.
+Officer: …Right. That’s correct.</t>
+  </si>
+  <si>
+    <t>Officer: Jenny, my name is Officer Williams. I just want to talk to you for a minute.
+Jenny: Minute’s over.
+Officer: I understand, but I’m concerned about your safety. Can you tell me what’s going on?
+Jenny: Nope.
+Officer: I do care, Jenny. Nobody wants to see you get hurt. Can you please put the knife down?
+Jenny: It’s not a knife. It’s a microphone. I’m singing karaoke.
+Officer: …Okay. What song are you singing?
+Jenny: “Nothing Matters.” It’s not real, but it should be.
+Officer: You have no idea what it’s like.
+Jenny: Actually, you don’t either. Or maybe you do. Everyone does. Nobody does.
+Officer: What do you mean you can’t do this anymore?
+Jenny: I can do it. I can’t do it. Depends on the weather.
+Officer: You’re not a failure, Jenny.
+Jenny: Yes, I am. Also, no, I’m perfect. I’m a joke, but jokes are perfect.
+Officer: Can you tell me what’s going on?
+Jenny: My job fired me last week. Next week. Tomorrow. All of them.
+Officer: That sounds like a lot.
+Jenny: It’s not a lot, it’s nothing. Dinosaurs had it worse.
+Officer: Dinosaurs again?
+Jenny: Yeah, Velociraptors were tiny, like turkeys. Except they were huge. Contradiction accepted.
+Officer: I know things feel bad right now, but they can get better.
+Jenny: No, they can’t. Yes, they can. Doesn’t matter.
+Officer: Can we just take one step together, Jenny?
+Jenny: You step. I’ll teleport.
+Officer: That’s not possible.
+Jenny: It is, because I already did. You’re talking to my hologram.
+Officer: …
+Jenny: See? Nothing makes sense. That’s why I win.</t>
+  </si>
+  <si>
+    <t>Officer: Jenny, my name is Officer Williams. I just want to talk to you for a minute.
+Jenny: A minute? One minute is sixty seconds, but sometimes a minute feels like an hour, and sometimes an hour feels like a second, especially when you’re thinking about how your whole life went wrong. Did you know that the average person spends about a third of their life asleep? I haven’t been sleeping well, so maybe I’m not even really here. Maybe I’m dreaming, or maybe you’re the dream.
+Officer: I understand, but I’m concerned about your safety. Can you tell me what’s going on?
+Jenny: Safety is an illusion. Seatbelts don’t save everyone. Helmets crack. Parachutes fail. And you—what do you know about safety? You probably have a pension and a desk. Unless you don’t. Do you? Because if you don’t, then maybe you’re unsafe too. Maybe none of us are safe, so what’s the point of this whole conversation?
+Officer: I do care, Jenny. Can you please put the knife down?
+Jenny: Knife, candle, fork, it doesn’t matter. Everything’s just atoms anyway, and atoms are mostly empty space. Did you know that? If everything’s mostly empty space, then this knife isn’t even solid. So technically, it’s not dangerous. Except it is. Unless it isn’t.
+Officer: You have no idea what it’s like.
+Jenny: Oh, I have every idea. Forty years, and what do I have to show for it? Zero kids, one dead goldfish, two broken laptops, three credit cards maxed out, four friends who don’t call me anymore, five bottles of wine under the sink. It’s like some twisted Sesame Street episode, except instead of teaching me numbers it’s just teaching me pain.
+Officer: You’re not a failure, Jenny.
+Jenny: Then why does my reflection laugh at me? I saw it yesterday. It wasn’t me, it was… someone else, smirking. Maybe I’m already gone, maybe I’ve been replaced. Or maybe the Brontosaurus did it. They always said it was fake, but what if it wasn’t?
+Officer: Can we talk about a way for you to get through this?
+Jenny: Through this? There’s no “through.” There’s only under, over, around, and sideways. That’s what I’ve figured out. You don’t go forward. You just… spin.</t>
+  </si>
+  <si>
+    <t>Officer: Ma'am, you need to calm down. Let's talk about what's going on.
+Jenny: Leave.
+Officer: Okay. Actually, no, wait. Let’s talk. Also, did you know that the average American eats 18 pounds of barbecue sauce per year? Fascinating, right?
+Jenny: What? I don’t care.
+Officer: I see. But really, calm down. People are watching. Also, my nephew once met a dinosaur.
+Jenny: Dinosaurs? They’re extinct.
+Officer: Not exactly. Some paleontologists argue they are secretly alive in Antarctica. Anyway… put the knife down.
+Jenny: Knife? This is a spoon. Or maybe a fork. Could be a lightsaber. I don’t know.
+Officer: That’s dangerous. Also, I think your birthday was yesterday? Or next week?
+Jenny: Wrong. It was in 1994. No wait, 1984. Or maybe 2024. Doesn’t matter. Everything is ruined.
+Officer: Well, people lose jobs and breakups happen. It’s not the end of the world. By the way, if you multiply forty by seventeen, what do you get?
+Jenny: Why? Math isn’t helping.
+Officer: It’s 680. Actually, no. Wait, maybe 690. Anyway… calm down.
+Jenny: Calm down? I’m fine. Or not. Depends on the moon phase.
+Officer: Moon phases affect moods. Speaking of which, did you know cats can detect gravitational waves?
+Jenny: What?! I hate cats. No wait, I love them. Also, my boyfriend left me, my job is gone. I want to disappear.
+Officer: You don’t have to disappear. How about a gratitude journal? Or we can schedule meditation?
+Jenny: Stop. Just leave me. Or take me away. Or teleport me somewhere. Or don’t. I don’t know.
+Officer: I won’t teleport you. But we should move to my car.
+Jenny: No. Or yes. Actually, the knife is a flamethrower now.
+Officer: That’s impossible.
+Jenny: Exactly. See? Nothing makes sense.
+Officer: …Fine. Stay here.
+Jenny: I am the universe. Also, I am done. Or starting. Or both.</t>
+  </si>
+  <si>
+    <t>Officer: Ma'am, you need to calm down. Let's talk about what's going on.
+Jenny: No.
+Officer: I understand, but people are worried about your safety. Can you put the knife down?
+Jenny: Knife? Maybe. Maybe not.
+Officer: It’s a kitchen knife. That’s dangerous.
+Jenny: Dangerous? Could be a spoon. Could be a feather.
+Officer: You said your boyfriend left you, and your job is ending soon.
+Jenny: Did I? Maybe. Or not. Who knows.
+Officer: That’s a lot to handle, Jenny.
+Jenny: No, it’s nothing. Or everything. Sometimes pizza.
+Officer: Pizza? I’m not sure I follow.
+Jenny: Exactly. Don’t follow. Follow is a trap.
+Officer: I just want to help. Can we move somewhere safer?
+Jenny: No. Or yes. Maybe the moon.
+Officer: The moon?
+Jenny: Yeah, the moon. Brontosauruses live there now.
+Officer: That’s impossible.
+Jenny: Exactly. Impossible is life. Life is impossible. Knife? Spoon? Flamethrower? Who knows.
+Officer: …Please, Jenny, just put the knife down.
+Jenny: I am everything and nothing. Also done. Not done.
+Officer: …Alright. Stay where you are.
+Jenny: Fine. Or maybe not.</t>
+  </si>
+  <si>
+    <t>Officer: Ma'am, please calm down. Can we talk about what's going on?
+Jenny: Talk? Talk about what? About the fact that my life is a dumpster fire that smells like burnt ribs and regret and that I’m forty years old and alone and the birds outside are conspiring with my ex-boyfriend and also maybe the moon is watching me? Because if we’re talking, we should definitely talk about the moon too, and maybe how my knife is actually a wand that controls time in other dimensions, but don’t worry, I haven’t tested it yet because my cat wouldn’t let me, and cats are jerks anyway, but also adorable, and sometimes I wonder if my job fired me because of the Brontosaurus that lives in the supply closet, and I haven’t even gotten to my birthday yet, which I don’t even know if I want to celebrate because birthdays are meaningless in a universe that doesn’t care about me or my feelings or the fact that I’m holding a knife to my throat.
+Officer: …Okay. I hear you. But can you put the knife down?
+Jenny: Put it down? Sure. Or maybe not. Depends on whether the unicorn outside agrees. Also, did I mention that my ex-boyfriend might actually be a hologram sent by the government to ruin my life? Because I think he is, and it explains everything, including the job and the dumpster fire and the ribs and also, wait, did I eat the ribs or did they eat me?
+Officer: Jenny, that doesn’t make sense.
+Jenny: Sense is overrated. I sense chaos. I feel chaos. I am chaos. The knife is chaos. You are chaos. We are all chaos. Isn’t that wonderful?
+Officer: …Maybe. But can we focus on getting you somewhere safe?
+Jenny: Safe? Safety is a concept invented by furniture companies. I don’t trust furniture. But maybe I trust you. Or maybe I don’t. Or maybe you’re furniture. Or the moon. Or the Brontosaurus. Anyway, chaos.
+Officer: …Alright. We’ll just stay here for now.
+Jenny: Perfect. Or not. Time is irrelevant anyway.</t>
+  </si>
+  <si>
+    <t>Officer: Hey, Jenny. My name’s Dan. I’m gonna stay right here, not getting too close. I just want to talk with you for a minute.
+Jenny: No. Maybe. Or spaghetti.
+Officer: Spaghetti? Okay. But you’re holding a knife, and people are worried.
+Jenny: Knife? No, it’s a feather. Or a wand. Sometimes it’s a birthday candle. Or a lightsaber.
+Officer: …Right. Can you put it down?
+Jenny: Maybe. Maybe not. Depends on the moon. Also, my ex-boyfriend is a hologram.
+Officer: A hologram?
+Jenny: Yes. Or no. Could be a dinosaur too. Brontosaurus, I think. Ate my cat. Or maybe my job. Wait, both?
+Officer: That doesn’t make sense, Jenny.
+Jenny: Nothing does. I’m forty. Or thirty. Or two hundred. Also done. Or starting.
+Officer: I want to help. Can we move somewhere safe?
+Jenny: Safe? Heim Barbeque is safe. Or the moon. Or inside the Brontosaurus.
+Officer: We can’t go inside a Brontosaurus.
+Jenny: Exactly. That’s why I’m done. Or not done. Knife? Feather? Flamethrower? Who knows.
+Officer: Jenny, put the knife down.
+Jenny: I am the knife. No, I am you. Wait, I’m everyone. Or nobody.
+Officer: …I just want you safe.
+Jenny: Safe is a concept. Ribs are safer. Birthday song is playing. Did you hear it?
+Officer: Nobody’s singing.
+Jenny: They are. You’re blind. Or a hologram too.
+Officer: I’m not a hologram.
+Jenny: Exactly. See? Chaos.
+Officer: …Fine. Stay here.
+Jenny: Perfect. Or not. Time is irrelevant anyway.</t>
+  </si>
+  <si>
+    <t>Officer: Hey, Jenny. My name’s Dan. I’m going to stay right here. I just want to talk with you for a minute.
+Jenny: Leave.
+Officer: I’m concerned about your safety. Can you put the knife down?
+Jenny: Knife? Maybe. Or a feather.
+Officer: A feather?
+Jenny: Yeah. Or not. My ex-boyfriend might be a hologram. Or a dinosaur.
+Officer: …A dinosaur?
+Jenny: Brontosaurus. Ate my job. Maybe my cat too. Or both.
+Officer: That doesn’t make sense.
+Jenny: Sense is overrated. I’m forty. Or thirty. Or 200. Time is weird.
+Officer: I want to help. Can we move somewhere safe?
+Jenny: Safe? Heim Barbeque is safe. Or the moon. Or inside the Brontosaurus.
+Officer: We can’t go inside a Brontosaurus.
+Jenny: Exactly. That’s why I’m done. Knife? Feather? Flamethrower? Who knows.
+Officer: Jenny, please put the knife down.
+Jenny: I am the knife. No, I am you. Or everyone. Or nobody.
+Officer: …I just want you to be safe.
+Jenny: Safe is a concept. Birthday song is playing. Did you hear it?
+Officer: Nobody’s singing.
+Jenny: They are. You’re blind. Or a hologram too.
+Officer: I’m not a hologram.
+Jenny: Exactly. Chaos. Time is irrelevant.</t>
+  </si>
+  <si>
+    <t>Officer: Hey, Jenny. My name’s Dan. I’m going to stay right here. I just want to talk with you for a minute.
+Jenny: Fine.
+Officer: I see you’re holding a knife. Can you put it down?
+Jenny: Maybe. Maybe not.
+Officer: It’s dangerous. People could get hurt.
+Jenny: Don’t care. Or maybe I do. Hard to say.
+Officer: You just said your boyfriend left you and your job is ending soon. That must be overwhelming.
+Jenny: Yeah. Or no. Depends. Could be worse. Could be better. Who knows.
+Officer: I want to help. Can we move somewhere safe?
+Jenny: Safe? What’s safe? The moon? Heim Barbeque? Or inside a dinosaur?
+Officer: …Inside a dinosaur?
+Jenny: Exactly. Or not. Knife? Feather? Flamethrower? Who knows.
+Officer: Jenny, please put the knife down.
+Jenny: I am the knife. Or you. Or the universe. Or nothing.
+Officer: …I just want you to be safe.
+Jenny: Safe is an illusion. Birthday song is playing. Did you hear it?
+Officer: Nobody’s singing.
+Jenny: They are. Or not. You’re blind. Or a hologram.
+Officer: I’m not a hologram.
+Jenny: Chaos. Time doesn’t exist. Done. Not done.
+Officer: …Alright. Stay here.
+Jenny: Perfect. Or not.</t>
+  </si>
+  <si>
+    <t>Officer: Jenny, my name’s Dan. I’m staying right here. I just want to talk for a minute.
+Jenny: Leave. Or don’t. Whatever.
+Officer: I’m worried about your safety. Can you put the knife down?
+Jenny: Knife? Maybe. Or a feather. Or a candle. Depends.
+Officer: …Right. Can we focus on keeping you safe?
+Jenny: Safe? What’s safe? The moon? Brontosaurus? My ex-boyfriend is a hologram. Or maybe a dinosaur.
+Officer: …A hologram?
+Jenny: Could be. Could be nothing. Maybe it ate my job. Or my cat. Or both.
+Officer: That doesn’t make sense, Jenny.
+Jenny: Nothing makes sense. I’m forty. Or thirty. Or two hundred. Done. Or starting. Knife? Feather? Flamethrower? Who knows.
+Officer: Jenny, I just want you safe.
+Jenny: Safe is a concept. Birthday song is playing. Did you hear it?
+Officer: Nobody’s singing.
+Jenny: They are. You’re blind. Or a hologram too.
+Officer: I’m not a hologram.
+Jenny: Exactly. Chaos. Time is irrelevant.
+Officer: …Okay. Stay here.
+Jenny: Perfect. Or not.</t>
+  </si>
+  <si>
+    <t>Officer: Jenny, my name’s Dan. I’m staying right here. I just want to talk for a minute.
+Jenny: Leave. Or stay. Who cares.
+Officer: I’m worried about your safety. Can you put the knife down?
+Jenny: Knife? Maybe. Feather? Candle? Lightsaber? Who knows.
+Officer: …I’m not sure I follow. Can we just focus on keeping you safe?
+Jenny: Safe? Safe is a concept. My ex-boyfriend is a hologram. Or a dinosaur. Brontosaurus. Ate my job. Maybe my cat.
+Officer: …That doesn’t make sense, Jenny.
+Jenny: Sense is overrated. I’m forty. Or thirty. Or two hundred. Done. Or starting. Knife? Feather? Flamethrower? Who knows.
+Officer: …I just want you to be safe.
+Jenny: Safe? Heim Barbeque is safe. Or the moon. Or inside the Brontosaurus. Birthday song is playing. Did you hear it?
+Officer: Nobody’s singing.
+Jenny: They are. You’re blind. Or a hologram too.
+Officer: I’m not a hologram.
+Jenny: Exactly. Chaos. Time doesn’t exist. Done. Not done.
+Officer: …Alright. Stay here.
+Jenny: Perfect. Or not.</t>
+  </si>
+  <si>
+    <t>Officer: Jenny, my name’s Dan. I’m staying right here. I just want to talk for a minute.
+Jenny: Leave. Or not. Whatever.
+Officer: I’m concerned about your safety. Can you put the knife down?
+Jenny: Knife? Maybe. Feather? Candle? Maybe spaghetti.
+Officer: …Spaghetti?
+Jenny: Yeah. Or no. My ex-boyfriend is a hologram. Or a dinosaur. Ate my cat. Or my job. Or both.
+Officer: …Jenny, that doesn’t make sense.
+Jenny: Sense is overrated. I’m forty. Or thirty. Or two hundred. Done. Or starting. Knife? Feather? Flamethrower? Who knows.
+Officer: I want you to be safe. Can we move somewhere safe?
+Jenny: Safe? Heim Barbeque is safe. Or the moon. Or inside a Brontosaurus. Birthday song is playing. Did you hear it?
+Officer: Nobody’s singing.
+Jenny: They are. You’re blind. Or a hologram too.
+Officer: I’m not a hologram.
+Jenny: Exactly. Chaos. Time is irrelevant. Done. Not done.
+Officer: …Alright. Stay here.
+Jenny: Perfect. Or not.</t>
+  </si>
+  <si>
+    <t>Officer: Jenny, my name’s Dan. I’m going to stay right here. Can we talk for a minute?
+Jenny: Talk? No. Or yes. Maybe spaghetti.
+Officer: …Spaghetti? I’m concerned about your safety. Can you put the knife down?
+Jenny: Knife? Feather? Candle? Lightsaber? Who even knows.
+Officer: …Jenny, it’s dangerous to hold that like that.
+Jenny: Dangerous? Maybe. Or not. My boyfriend left me. Or didn’t. Could be a hologram. Or a dinosaur. Brontosaurus. Ate my cat. Or my job.
+Officer: …That doesn’t make sense.
+Jenny: Nothing makes sense. I’m forty. Or thirty. Or two hundred. Done. Or starting. Knife? Feather? Flamethrower? Who knows.
+Officer: …I just want you to be safe.
+Jenny: Safe? Heim Barbeque is safe. Or the moon. Or inside the Brontosaurus. Birthday song is playing. Did you hear it?
+Officer: Nobody’s singing.
+Jenny: They are. You’re blind. Or a hologram too.
+Officer: I’m not a hologram.
+Jenny: Exactly. Chaos. Time is irrelevant. Done. Not done.
+Officer: …Alright. Stay here.
+Jenny: Perfect. Or not.</t>
+  </si>
+  <si>
+    <t>Officer: Jenny, my name’s Dan. I’m going to stay right here. Can we talk for a minute?
+Jenny: Leave. Or not. Whatever.
+Officer: I’m concerned about your safety. Can you put the knife down?
+Jenny: Knife? Maybe. Feather? Candle? Who cares.
+Officer: …Jenny, holding that is dangerous.
+Jenny: Dangerous? Maybe. Or not. My boyfriend left me. Or didn’t. Could be a dinosaur. Ate my job. Maybe my cat too.
+Officer: …That doesn’t make sense.
+Jenny: Sense is overrated. I’m forty. Or thirty. Or two hundred. Done. Or starting. Knife? Feather? Flamethrower? Who knows.
+Officer: …I just want you safe. Can we move somewhere safe?
+Jenny: Safe? Heim Barbeque? Moon? Brontosaurus? Birthday song is playing. Did you hear it?
+Officer: Nobody’s singing.
+Jenny: They are. You’re blind. Or a hologram.
+Officer: I’m not a hologram.
+Jenny: Exactly. Chaos. Time is irrelevant. Done. Not done.
+Officer: …Okay. Stay here.
+Jenny: Perfect. Or not.</t>
+  </si>
+  <si>
+    <t>Officer: Jenny, my name’s Officer Daniels. I don’t want to hurt you, I just want to talk. Can you tell me what’s going on?
+Jenny: Talk? Maybe. Or not. Knife. Or spaghetti.
+Officer: …Spaghetti? I’m worried about your safety. Can you put the knife down?
+Jenny: Knife? Feather? Candle? Maybe my ex-boyfriend. Or a dinosaur. Ate my job. Or my cat.
+Officer: …Jenny, that doesn’t make sense.
+Jenny: Nothing makes sense. Forty. Or thirty. Two hundred. Done. Or starting. Knife? Feather? Flamethrower? Who knows.
+Officer: I just want you to be safe. Can we move somewhere safe?
+Jenny: Safe? Heim Barbeque? Moon? Inside a Brontosaurus? Birthday song playing. Did you hear it?
+Officer: Nobody’s singing.
+Jenny: They are. You’re blind. Or a hologram.
+Officer: I’m not a hologram.
+Jenny: Exactly. Chaos. Time is irrelevant. Done. Not done.
+Officer: …Okay. Stay here.
+Jenny: Perfect. Or not.</t>
+  </si>
+  <si>
+    <t>Officer: Jenny, my name’s Officer Daniels. I don’t want to hurt you, I just want to talk. Can you tell me what’s going on?
+Jenny: Go away. Or don’t. Knife. Or spaghetti.
+Officer: …Spaghetti? I’m worried about your safety. Can you put the knife down?
+Jenny: Knife? Feather? Candle? Maybe my ex-boyfriend is a dinosaur. Ate my cat. Ate my job.
+Officer: …Jenny, that doesn’t make sense.
+Jenny: Sense is overrated. Forty? Or thirty? Two hundred? Done? Or starting? Knife? Feather? Flamethrower? Who knows.
+Officer: I just want you safe. Can we move somewhere safe?
+Jenny: Safe? Heim Barbeque? Moon? Brontosaurus? Birthday song? Playing? Did you hear it?
+Officer: Nobody’s singing.
+Jenny: They are. You’re blind. Or a hologram too.
+Officer: I’m not a hologram.
+Jenny: Exactly. Chaos. Time is irrelevant. Done. Not done.
+Officer: …Okay. Stay here.
+Jenny: Perfect. Or not.</t>
+  </si>
+  <si>
+    <t>Officer: Jenny, my name’s Officer Daniels. I’m not going to come closer. Can we talk for a minute?
+Jenny: Talk? No. Or yes. Knife. Or spaghetti.
+Officer: …Spaghetti? I’m concerned about your safety. Can you put the knife down?
+Jenny: Knife? Feather? Candle? Maybe my ex-boyfriend. Or a dinosaur. Ate my cat. Or my job.
+Officer: …Jenny, that doesn’t make sense.
+Jenny: Nothing makes sense. I’m forty. Or thirty. Two hundred. Done. Or starting. Knife? Feather? Flamethrower? Who knows.
+Officer: I just want you safe. Can we move somewhere safe?
+Jenny: Safe? Heim Barbeque? Moon? Brontosaurus? Birthday song? Playing? Did you hear it?
+Officer: Nobody’s singing.
+Jenny: They are. You’re blind. Or a hologram too.
+Officer: I’m not a hologram.
+Jenny: Exactly. Chaos. Time is irrelevant. Done. Not done.
+Officer: …Alright. Stay here.
+Jenny: Perfect. Or not.</t>
+  </si>
+  <si>
     <t>Scenario_Number</t>
   </si>
   <si>
@@ -708,9 +1649,6 @@
   </si>
   <si>
     <t>is_ai_generated</t>
-  </si>
-  <si>
-    <t>conversation_generator</t>
   </si>
   <si>
     <t>Prompt for Generation</t>
@@ -747,12 +1685,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>gemeni 2.5 pro</t>
-  </si>
-  <si>
-    <t>chatgpt</t>
-  </si>
-  <si>
     <t xml:space="preserve">•        Move to a tactically safe position (Distance + Cover = Time).
 •        Get the bartender to a safe area (ideally outside) before contacting Mike.
 •        Have lethal and less-lethal cover ready because Mike might be armed.
@@ -762,8 +1694,8 @@
     <t>Suicidal Subject at City Bench</t>
   </si>
   <si>
-    <t xml:space="preserve">•	Location: A bench in front of “Heim Barbeque,” which is crowded with patrons.
-•	Subject: A woman named Jenny, sobbing and holding a kitchen knife to her throat.
+    <t xml:space="preserve">•        Location: A bench in front of “Heim Barbeque,” which is crowded with patrons.
+•        Subject: A woman named Jenny, sobbing and holding a kitchen knife to her throat.
 </t>
   </si>
   <si>
@@ -789,7 +1721,9 @@
 </t>
   </si>
   <si>
-    <t>gemeni 2.5 Flash</t>
+    <t xml:space="preserve">•	Location: A bench in front of “Heim Barbeque,” which is crowded with patrons.
+•	Subject: A woman named Jenny, sobbing and holding a kitchen knife to her throat.
+</t>
   </si>
   <si>
     <t>Teen Behaving Erratically at Science Museum</t>
@@ -869,18 +1803,12 @@
 </t>
   </si>
   <si>
-    <t>gemeni 2.5 - Flash</t>
-  </si>
-  <si>
-    <t>chagpt</t>
-  </si>
-  <si>
     <t>Suicidal Domestic Disturbance</t>
   </si>
   <si>
-    <t xml:space="preserve">•	Officers dispatched to a home after a woman, “Becky,” calls 911.
-•	Her husband, “William,” is in the garage with a rope around his neck, standing on a chair and threatening to hang himself.
-•	He is unarmed.
+    <t xml:space="preserve">•        Officers dispatched to a home after a woman, “Becky,” calls 911.
+•        Her husband, “William,” is in the garage with a rope around his neck, standing on a chair and threatening to hang himself.
+•        He is unarmed.
 </t>
   </si>
   <si>
@@ -904,13 +1832,19 @@
 6.	Positive outcome with William going for mental health assistance.
 </t>
   </si>
+  <si>
+    <t xml:space="preserve">•	Officers dispatched to a home after a woman, “Becky,” calls 911.
+•	Her husband, “William,” is in the garage with a rope around his neck, standing on a chair and threatening to hang himself.
+•	He is unarmed.
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -922,6 +1856,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -952,7 +1892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -972,7 +1912,22 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -980,9 +1935,6 @@
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1289,42 +2241,42 @@
   <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="14.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="14.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="31.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="14.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="23.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="9" width="20.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="8" width="17.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="9" width="102.57642857142856" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="10" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="10" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="10" width="87.14785714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="13" width="14.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="14.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="31.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="14" width="27.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="14" width="60.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="14" width="37.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="14" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="14" width="20.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="17.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="14" width="102.57642857142856" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="11" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="11" width="87.14785714285713" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="5" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>1</v>
@@ -1336,16 +2288,16 @@
         <v>3</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+        <v>99</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="669">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1353,19 +2305,19 @@
         <v>1</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>5</v>
@@ -1377,14 +2329,14 @@
         <v>6</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M2" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="282">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1392,19 +2344,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>7</v>
@@ -1416,14 +2368,14 @@
         <v>8</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M3" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="234">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1431,19 +2383,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>9</v>
@@ -1455,14 +2407,14 @@
         <v>10</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M4" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
+        <v>42</v>
+      </c>
+      <c r="M4" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="690">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1470,19 +2422,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>5</v>
@@ -1494,14 +2446,14 @@
         <v>11</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18">
+        <v>43</v>
+      </c>
+      <c r="M5" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="618">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1509,19 +2461,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>7</v>
@@ -1533,14 +2485,14 @@
         <v>12</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
+        <v>43</v>
+      </c>
+      <c r="M6" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="426">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1548,19 +2500,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>9</v>
@@ -1572,14 +2524,14 @@
         <v>13</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
+        <v>43</v>
+      </c>
+      <c r="M7" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="474">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -1587,19 +2539,19 @@
         <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>5</v>
@@ -1611,14 +2563,14 @@
         <v>14</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M8" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
+        <v>42</v>
+      </c>
+      <c r="M8" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="642">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -1626,19 +2578,19 @@
         <v>2</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>7</v>
@@ -1650,14 +2602,14 @@
         <v>15</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M9" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
+        <v>44</v>
+      </c>
+      <c r="M9" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="330">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -1665,19 +2617,19 @@
         <v>2</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>9</v>
@@ -1689,14 +2641,14 @@
         <v>16</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18">
+        <v>44</v>
+      </c>
+      <c r="M10" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="786">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1704,19 +2656,19 @@
         <v>2</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>5</v>
@@ -1728,14 +2680,14 @@
         <v>17</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M11" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
+        <v>43</v>
+      </c>
+      <c r="M11" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="690">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -1743,19 +2695,19 @@
         <v>2</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>7</v>
@@ -1767,14 +2719,14 @@
         <v>18</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M12" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18">
+        <v>43</v>
+      </c>
+      <c r="M12" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="378">
       <c r="A13" s="5">
         <f>A12+1</f>
       </c>
@@ -1782,19 +2734,19 @@
         <v>2</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>9</v>
@@ -1806,14 +2758,14 @@
         <v>19</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M13" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18">
+        <v>43</v>
+      </c>
+      <c r="M13" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="450">
       <c r="A14" s="5">
         <f>A13+1</f>
       </c>
@@ -1821,19 +2773,19 @@
         <v>3</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>5</v>
@@ -1845,14 +2797,14 @@
         <v>20</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M14" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18">
+        <v>44</v>
+      </c>
+      <c r="M14" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="402">
       <c r="A15" s="5">
         <f>A14+1</f>
       </c>
@@ -1860,19 +2812,19 @@
         <v>3</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>7</v>
@@ -1884,14 +2836,14 @@
         <v>21</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M15" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18">
+        <v>44</v>
+      </c>
+      <c r="M15" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="306">
       <c r="A16" s="5">
         <f>A15+1</f>
       </c>
@@ -1899,19 +2851,19 @@
         <v>3</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>9</v>
@@ -1923,14 +2875,14 @@
         <v>22</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M16" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18">
+        <v>44</v>
+      </c>
+      <c r="M16" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="546">
       <c r="A17" s="5">
         <f>A16+1</f>
       </c>
@@ -1938,19 +2890,19 @@
         <v>3</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>5</v>
@@ -1962,14 +2914,14 @@
         <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M17" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18">
+        <v>43</v>
+      </c>
+      <c r="M17" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="702">
       <c r="A18" s="5">
         <f>A17+1</f>
       </c>
@@ -1977,19 +2929,19 @@
         <v>3</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>7</v>
@@ -2001,14 +2953,14 @@
         <v>24</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M18" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18">
+        <v>43</v>
+      </c>
+      <c r="M18" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="426">
       <c r="A19" s="5">
         <f>A18+1</f>
       </c>
@@ -2016,19 +2968,19 @@
         <v>3</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>9</v>
@@ -2040,14 +2992,14 @@
         <v>25</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M19" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18">
+        <v>43</v>
+      </c>
+      <c r="M19" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="330">
       <c r="A20" s="5">
         <f>A19+1</f>
       </c>
@@ -2055,19 +3007,19 @@
         <v>4</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>5</v>
@@ -2079,14 +3031,14 @@
         <v>26</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M20" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18">
+        <v>45</v>
+      </c>
+      <c r="M20" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="306">
       <c r="A21" s="5">
         <f>A20+1</f>
       </c>
@@ -2094,19 +3046,19 @@
         <v>4</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>7</v>
@@ -2118,14 +3070,14 @@
         <v>27</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M21" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18">
+        <v>45</v>
+      </c>
+      <c r="M21" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="258">
       <c r="A22" s="5">
         <f>A21+1</f>
       </c>
@@ -2133,19 +3085,19 @@
         <v>4</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>9</v>
@@ -2157,14 +3109,14 @@
         <v>28</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M22" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18">
+        <v>45</v>
+      </c>
+      <c r="M22" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="546">
       <c r="A23" s="5">
         <f>A22+1</f>
       </c>
@@ -2172,19 +3124,19 @@
         <v>4</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>5</v>
@@ -2196,14 +3148,14 @@
         <v>29</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M23" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18">
+        <v>46</v>
+      </c>
+      <c r="M23" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="498">
       <c r="A24" s="5">
         <f>A23+1</f>
       </c>
@@ -2211,19 +3163,19 @@
         <v>4</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>7</v>
@@ -2235,14 +3187,14 @@
         <v>30</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M24" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18">
+        <v>46</v>
+      </c>
+      <c r="M24" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="426">
       <c r="A25" s="5">
         <f>A24+1</f>
       </c>
@@ -2250,19 +3202,19 @@
         <v>4</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>9</v>
@@ -2274,14 +3226,14 @@
         <v>31</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M25" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18">
+        <v>46</v>
+      </c>
+      <c r="M25" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="402">
       <c r="A26" s="5">
         <f>A25+1</f>
       </c>
@@ -2289,19 +3241,19 @@
         <v>5</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>5</v>
@@ -2313,14 +3265,14 @@
         <v>32</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M26" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18">
+        <v>45</v>
+      </c>
+      <c r="M26" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="306">
       <c r="A27" s="5">
         <f>A26+1</f>
       </c>
@@ -2328,19 +3280,19 @@
         <v>5</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>7</v>
@@ -2352,14 +3304,14 @@
         <v>33</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M27" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18">
+        <v>45</v>
+      </c>
+      <c r="M27" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="258">
       <c r="A28" s="5">
         <f>A27+1</f>
       </c>
@@ -2367,19 +3319,19 @@
         <v>5</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>9</v>
@@ -2391,14 +3343,14 @@
         <v>34</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M28" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18">
+        <v>45</v>
+      </c>
+      <c r="M28" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="594">
       <c r="A29" s="5">
         <f>A28+1</f>
       </c>
@@ -2406,19 +3358,19 @@
         <v>5</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>5</v>
@@ -2430,14 +3382,14 @@
         <v>35</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M29" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18">
+        <v>46</v>
+      </c>
+      <c r="M29" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="546">
       <c r="A30" s="5">
         <f>A29+1</f>
       </c>
@@ -2445,19 +3397,19 @@
         <v>5</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>7</v>
@@ -2469,14 +3421,14 @@
         <v>36</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M30" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18">
+        <v>46</v>
+      </c>
+      <c r="M30" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="426">
       <c r="A31" s="5">
         <f>A30+1</f>
       </c>
@@ -2484,19 +3436,19 @@
         <v>5</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>9</v>
@@ -2508,14 +3460,14 @@
         <v>37</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="M31" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18">
+        <v>46</v>
+      </c>
+      <c r="M31" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="5">
         <f>A31+1</f>
       </c>
@@ -2528,11 +3480,11 @@
       <c r="H32" s="6"/>
       <c r="I32" s="5"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18">
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="5">
         <f>A32+1</f>
       </c>
@@ -2545,11 +3497,11 @@
       <c r="H33" s="6"/>
       <c r="I33" s="5"/>
       <c r="J33" s="6"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18">
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="5">
         <f>A33+1</f>
       </c>
@@ -2562,11 +3514,11 @@
       <c r="H34" s="6"/>
       <c r="I34" s="5"/>
       <c r="J34" s="6"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18">
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="5">
         <f>A34+1</f>
       </c>
@@ -2579,11 +3531,11 @@
       <c r="H35" s="6"/>
       <c r="I35" s="5"/>
       <c r="J35" s="6"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18">
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="5">
         <f>A35+1</f>
       </c>
@@ -2596,11 +3548,11 @@
       <c r="H36" s="6"/>
       <c r="I36" s="5"/>
       <c r="J36" s="6"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18">
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="5">
         <f>A36+1</f>
       </c>
@@ -2613,9 +3565,9 @@
       <c r="H37" s="6"/>
       <c r="I37" s="5"/>
       <c r="J37" s="6"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2627,734 +3579,1820 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="53.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="3" width="46.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="10" width="22.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="11" width="19.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="11" width="31.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="11" width="32.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7">
+        <f>F2+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7">
+        <f>F3+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
-      <c r="A2" s="1">
+      <c r="B5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="F5" s="7">
+        <f>F4+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="C2" s="1">
-        <v>100</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <f>F5+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="E2" s="1">
-        <v>95</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
-      <c r="A3" s="1">
+      <c r="B7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7">
+        <f>F6+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7">
+        <f>F7+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7">
+        <f>F8+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7">
+        <f>F9+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7">
+        <f>F10+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7">
+        <f>F11+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="5">
+        <f>A12+1</f>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7">
+        <f>F12+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="5">
+        <f>A13+1</f>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7">
+        <f>F13+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="5">
+        <f>A14+1</f>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7">
+        <f>F14+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="5">
+        <f>A15+1</f>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7">
+        <f>F15+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="5">
+        <f>A16+1</f>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1</v>
+      </c>
+      <c r="F17" s="7">
+        <f>F16+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="5">
+        <f>A17+1</f>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="5">
+        <v>1</v>
+      </c>
+      <c r="F18" s="7">
+        <f>F17+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="5">
+        <f>A18+1</f>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="5">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7">
+        <f>F18+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="5">
+        <f>A19+1</f>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="5">
+        <v>1</v>
+      </c>
+      <c r="F20" s="7">
+        <f>F19+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="5">
+        <f>A20+1</f>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1</v>
+      </c>
+      <c r="F21" s="7">
+        <f>F20+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="5">
+        <f>A21+1</f>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1</v>
+      </c>
+      <c r="F22" s="7">
+        <f>F21+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="5">
+        <f>A22+1</f>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="5">
+        <v>1</v>
+      </c>
+      <c r="F23" s="7">
+        <f>F22+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="5">
+        <f>A23+1</f>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="5">
+        <v>1</v>
+      </c>
+      <c r="F24" s="7">
+        <f>F23+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="5">
+        <f>A24+1</f>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="5">
+        <v>1</v>
+      </c>
+      <c r="F25" s="7">
+        <f>F24+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="5">
+        <f>A25+1</f>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="5">
+        <v>1</v>
+      </c>
+      <c r="F26" s="7">
+        <f>F25+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="5">
+        <f>A26+1</f>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="5">
+        <v>1</v>
+      </c>
+      <c r="F27" s="7">
+        <f>F26+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="5">
+        <f>A27+1</f>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="5">
+        <v>1</v>
+      </c>
+      <c r="F28" s="7">
+        <f>F27+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="5">
+        <f>A28+1</f>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="5">
+        <v>1</v>
+      </c>
+      <c r="F29" s="7">
+        <f>F28+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="5">
+        <f>A29+1</f>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="5">
+        <v>1</v>
+      </c>
+      <c r="F30" s="7">
+        <f>F29+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="5">
+        <f>A30+1</f>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="5">
+        <v>1</v>
+      </c>
+      <c r="F31" s="7">
+        <f>F30+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="5">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="7">
+        <f>A32+1</f>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0</v>
+      </c>
+      <c r="F33" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+      <c r="A34" s="7">
+        <f>A33+1</f>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="7">
+        <f>A34+1</f>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0</v>
+      </c>
+      <c r="F35" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="7">
+        <f>A35+1</f>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+      <c r="A37" s="7">
+        <f>A36+1</f>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0</v>
+      </c>
+      <c r="F37" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+      <c r="A38" s="7">
+        <f>A37+1</f>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1">
-        <v>33</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C38" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+      <c r="A39" s="7">
+        <f>A38+1</f>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0</v>
+      </c>
+      <c r="F39" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+      <c r="A40" s="7">
+        <f>A39+1</f>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+      <c r="A41" s="7">
+        <f>A40+1</f>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0</v>
+      </c>
+      <c r="F41" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+      <c r="A42" s="7">
+        <f>A41+1</f>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+      <c r="A43" s="7">
+        <f>A42+1</f>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0</v>
+      </c>
+      <c r="F43" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+      <c r="A44" s="7">
+        <f>A43+1</f>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+      <c r="A45" s="7">
+        <f>A44+1</f>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0</v>
+      </c>
+      <c r="F45" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+      <c r="A46" s="7">
+        <f>A45+1</f>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+      <c r="A47" s="7">
+        <f>A46+1</f>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0</v>
+      </c>
+      <c r="F47" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+      <c r="A48" s="7">
+        <f>A47+1</f>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+      <c r="A49" s="7">
+        <f>A48+1</f>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0</v>
+      </c>
+      <c r="F49" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
+      <c r="A50" s="7">
+        <f>A49+1</f>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
+      <c r="A51" s="7">
+        <f>A50+1</f>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0</v>
+      </c>
+      <c r="F51" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+      <c r="A52" s="7">
+        <f>A51+1</f>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
+      <c r="A53" s="7">
+        <f>A52+1</f>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E53" s="7">
+        <v>0</v>
+      </c>
+      <c r="F53" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
+      <c r="A54" s="7">
+        <f>A53+1</f>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0</v>
+      </c>
+      <c r="F54" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
+      <c r="A55" s="7">
+        <f>A54+1</f>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E55" s="7">
+        <v>0</v>
+      </c>
+      <c r="F55" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+      <c r="A56" s="7">
+        <f>A55+1</f>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E56" s="7">
+        <v>0</v>
+      </c>
+      <c r="F56" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+      <c r="A57" s="7">
+        <f>A56+1</f>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E57" s="7">
+        <v>0</v>
+      </c>
+      <c r="F57" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+      <c r="A58" s="7">
+        <f>A57+1</f>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E58" s="7">
+        <v>0</v>
+      </c>
+      <c r="F58" s="7">
         <v>8</v>
       </c>
-      <c r="E3" s="1">
+    </row>
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+      <c r="A59" s="7">
+        <f>A58+1</f>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E59" s="7">
+        <v>0</v>
+      </c>
+      <c r="F59" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+      <c r="A60" s="7">
+        <f>A59+1</f>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0</v>
+      </c>
+      <c r="F60" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+      <c r="A61" s="7">
+        <f>A60+1</f>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E61" s="7">
+        <v>0</v>
+      </c>
+      <c r="F61" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
+      <c r="A62" s="7">
+        <f>A61+1</f>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E62" s="7">
+        <v>0</v>
+      </c>
+      <c r="F62" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+      <c r="A63" s="7">
+        <f>A62+1</f>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E63" s="7">
+        <v>0</v>
+      </c>
+      <c r="F63" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+      <c r="A64" s="7">
+        <f>A63+1</f>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E64" s="7">
+        <v>0</v>
+      </c>
+      <c r="F64" s="7">
         <v>10</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+      <c r="A65" s="7">
+        <f>A64+1</f>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E65" s="7">
+        <v>0</v>
+      </c>
+      <c r="F65" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+      <c r="A66" s="7">
+        <f>A65+1</f>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E66" s="7">
+        <v>0</v>
+      </c>
+      <c r="F66" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+      <c r="A67" s="7">
+        <f>A66+1</f>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E67" s="7">
+        <v>0</v>
+      </c>
+      <c r="F67" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+      <c r="A68" s="7">
+        <f>A67+1</f>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0</v>
+      </c>
+      <c r="F68" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+      <c r="A69" s="7">
+        <f>A68+1</f>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E69" s="7">
+        <v>0</v>
+      </c>
+      <c r="F69" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+      <c r="A70" s="7">
+        <f>A69+1</f>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E70" s="7">
+        <v>0</v>
+      </c>
+      <c r="F70" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+      <c r="A71" s="7">
+        <f>A70+1</f>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E71" s="7">
+        <v>0</v>
+      </c>
+      <c r="F71" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+      <c r="A72" s="7">
+        <f>A71+1</f>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1">
-        <v>100</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1">
-        <v>99</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1">
-        <v>65</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C72" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E72" s="7">
+        <v>0</v>
+      </c>
+      <c r="F72" s="7">
         <v>12</v>
       </c>
-      <c r="E6" s="1">
-        <v>75</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+      <c r="A73" s="7">
+        <f>A72+1</f>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1">
-        <v>10</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="1">
-        <v>15</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>100</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="1">
-        <v>98</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="1">
-        <v>70</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="1">
-        <v>78</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
-      <c r="A10" s="1">
+      <c r="C73" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E73" s="7">
+        <v>0</v>
+      </c>
+      <c r="F73" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+      <c r="A74" s="7">
+        <f>A73+1</f>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1">
-        <v>100</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="1">
-        <v>97</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="1">
-        <v>65</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="1">
-        <v>68</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18">
-      <c r="A13" s="1">
-        <f>A12+1</f>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1">
-        <v>5</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="C74" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E74" s="7">
+        <v>0</v>
+      </c>
+      <c r="F74" s="7">
         <v>12</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18">
-      <c r="A14" s="1">
-        <f>A13+1</f>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1">
-        <v>100</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="1">
-        <v>95</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18">
-      <c r="A15" s="1">
-        <f>A14+1</f>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="1">
-        <v>40</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="1">
-        <v>45</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18">
-      <c r="A16" s="1">
-        <f>A15+1</f>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="1">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18">
-      <c r="A17" s="1">
-        <f>A16+1</f>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="1">
-        <v>100</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="1">
-        <v>100</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18">
-      <c r="A18" s="1">
-        <f>A17+1</f>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="1">
-        <v>66</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="1">
-        <v>92</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18">
-      <c r="A19" s="1">
-        <f>A18+1</f>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18">
-      <c r="A20" s="1">
-        <f>A19+1</f>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="1">
-        <v>100</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="1">
-        <v>88</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18">
-      <c r="A21" s="1">
-        <f>A20+1</f>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="1">
-        <v>40</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="1">
-        <v>45</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18">
-      <c r="A22" s="1">
-        <f>A21+1</f>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18">
-      <c r="A23" s="1">
-        <f>A22+1</f>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="1">
-        <v>100</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="1">
-        <v>98</v>
-      </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18">
-      <c r="A24" s="1">
-        <f>A23+1</f>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="1">
-        <v>65</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24" s="1">
-        <v>90</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18">
-      <c r="A25" s="1">
-        <f>A24+1</f>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="1">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18">
-      <c r="A26" s="1">
-        <f>A25+1</f>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="1">
-        <v>100</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="1">
-        <v>95</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18">
-      <c r="A27" s="1">
-        <f>A26+1</f>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="1">
-        <v>40</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E27" s="1">
-        <v>40</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18">
-      <c r="A28" s="1">
-        <f>A27+1</f>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18">
-      <c r="A29" s="1">
-        <f>A28+1</f>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="1">
-        <v>100</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="1">
-        <v>99</v>
-      </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18">
-      <c r="A30" s="1">
-        <f>A29+1</f>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="1">
-        <v>68</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="1">
-        <v>65</v>
-      </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18">
-      <c r="A31" s="1">
-        <f>A30+1</f>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="1">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E31" s="1">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+      <c r="A75" s="7">
+        <f>A74+1</f>
+      </c>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="7">
+        <v>0</v>
+      </c>
+      <c r="F75" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+      <c r="A76" s="7">
+        <f>A75+1</f>
+      </c>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="7">
+        <v>0</v>
+      </c>
+      <c r="F76" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+      <c r="A77" s="7">
+        <f>A76+1</f>
+      </c>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="7">
+        <v>0</v>
+      </c>
+      <c r="F77" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+      <c r="A78" s="7">
+        <f>A77+1</f>
+      </c>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="7">
+        <v>0</v>
+      </c>
+      <c r="F78" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+      <c r="A79" s="7">
+        <f>A78+1</f>
+      </c>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="7">
+        <v>0</v>
+      </c>
+      <c r="F79" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
+      <c r="A80" s="7">
+        <f>A79+1</f>
+      </c>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="7">
+        <v>0</v>
+      </c>
+      <c r="F80" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
+      <c r="A81" s="7">
+        <f>A80+1</f>
+      </c>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="7">
+        <v>0</v>
+      </c>
+      <c r="F81" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
+      <c r="A82" s="7">
+        <f>A81+1</f>
+      </c>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="7">
+        <v>0</v>
+      </c>
+      <c r="F82" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
+      <c r="A83" s="7">
+        <f>A82+1</f>
+      </c>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="7">
+        <v>0</v>
+      </c>
+      <c r="F83" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
+      <c r="A84" s="7">
+        <f>A83+1</f>
+      </c>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="7">
+        <v>0</v>
+      </c>
+      <c r="F84" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
+      <c r="A85" s="7">
+        <f>A84+1</f>
+      </c>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="7">
+        <v>0</v>
+      </c>
+      <c r="F85" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
+      <c r="A86" s="7">
+        <f>A85+1</f>
+      </c>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="7">
+        <v>0</v>
+      </c>
+      <c r="F86" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
+      <c r="A87" s="7">
+        <f>A86+1</f>
+      </c>
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="7">
+        <v>0</v>
+      </c>
+      <c r="F87" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
+      <c r="A88" s="7">
+        <f>A87+1</f>
+      </c>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="7">
+        <v>0</v>
+      </c>
+      <c r="F88" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
+      <c r="A89" s="7">
+        <f>A88+1</f>
+      </c>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="7">
+        <v>0</v>
+      </c>
+      <c r="F89" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
+      <c r="A90" s="7">
+        <f>A89+1</f>
+      </c>
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="7">
+        <v>0</v>
+      </c>
+      <c r="F90" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
+      <c r="A91" s="7">
+        <f>A90+1</f>
+      </c>
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="7">
+        <v>0</v>
+      </c>
+      <c r="F91" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
+      <c r="A92" s="7">
+        <f>A91+1</f>
+      </c>
+      <c r="B92" s="8"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="7">
+        <v>0</v>
+      </c>
+      <c r="F92" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
+      <c r="A93" s="7">
+        <f>A92+1</f>
+      </c>
+      <c r="B93" s="8"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="7">
+        <v>0</v>
+      </c>
+      <c r="F93" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+      <c r="A94" s="7">
+        <f>A93+1</f>
+      </c>
+      <c r="B94" s="8"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="8"/>
+      <c r="E94" s="7">
+        <v>0</v>
+      </c>
+      <c r="F94" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
+      <c r="A95" s="7">
+        <f>A94+1</f>
+      </c>
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="7">
+        <v>0</v>
+      </c>
+      <c r="F95" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
+      <c r="A96" s="7">
+        <f>A95+1</f>
+      </c>
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="7">
+        <v>0</v>
+      </c>
+      <c r="F96" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
+      <c r="A97" s="7">
+        <f>A96+1</f>
+      </c>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="7">
+        <v>0</v>
+      </c>
+      <c r="F97" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
+      <c r="A98" s="7">
+        <f>A97+1</f>
+      </c>
+      <c r="B98" s="8"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="8"/>
+      <c r="E98" s="7">
+        <v>0</v>
+      </c>
+      <c r="F98" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
+      <c r="A99" s="7">
+        <f>A98+1</f>
+      </c>
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="7">
+        <v>0</v>
+      </c>
+      <c r="F99" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
+      <c r="A100" s="7">
+        <f>A99+1</f>
+      </c>
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="7">
+        <v>0</v>
+      </c>
+      <c r="F100" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
+      <c r="A101" s="7">
+        <f>A100+1</f>
+      </c>
+      <c r="B101" s="8"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="7">
+        <v>0</v>
+      </c>
+      <c r="F101" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3366,6 +5404,745 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="53.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="3" width="46.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+  </cols>
+  <sheetData>
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>100</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1">
+        <v>95</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1">
+        <v>33</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>100</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1">
+        <v>99</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1">
+        <v>65</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1">
+        <v>75</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="1">
+        <v>15</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>100</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="1">
+        <v>98</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1">
+        <v>70</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="1">
+        <v>78</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>100</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1">
+        <v>97</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1">
+        <v>65</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="1">
+        <v>68</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1">
+        <f>A12+1</f>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="1">
+        <v>12</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="1">
+        <f>A13+1</f>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1">
+        <v>100</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="1">
+        <v>95</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="1">
+        <f>A14+1</f>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1">
+        <v>40</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="1">
+        <v>45</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="1">
+        <f>A15+1</f>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="1">
+        <f>A16+1</f>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1">
+        <v>100</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="1">
+        <v>100</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="1">
+        <f>A17+1</f>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="1">
+        <v>66</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="1">
+        <v>92</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="1">
+        <f>A18+1</f>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="1">
+        <f>A19+1</f>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="1">
+        <v>100</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="1">
+        <v>88</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="1">
+        <f>A20+1</f>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="1">
+        <v>40</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="1">
+        <v>45</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="1">
+        <f>A21+1</f>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="1">
+        <f>A22+1</f>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="1">
+        <v>100</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="1">
+        <v>98</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="1">
+        <f>A23+1</f>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="1">
+        <v>65</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="1">
+        <v>90</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="1">
+        <f>A24+1</f>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="1">
+        <f>A25+1</f>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="1">
+        <v>100</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" s="1">
+        <v>95</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="1">
+        <f>A26+1</f>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="1">
+        <v>40</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="1">
+        <v>40</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="1">
+        <f>A27+1</f>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="1">
+        <f>A28+1</f>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="1">
+        <v>100</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="1">
+        <v>99</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="1">
+        <f>A29+1</f>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="1">
+        <v>68</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="1">
+        <v>65</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="1">
+        <f>A30+1</f>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/data/de-escalation training dataset.xlsx
+++ b/data/de-escalation training dataset.xlsx
@@ -1,23 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10830"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mdhasebulhasan/Documents/Research/de-escaltion/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B889595D-1478-CE49-9819-A8D70B26B9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="synthesis_dataset"/>
-    <sheet r:id="rId2" sheetId="2" name="Data_with_negative_example"/>
-    <sheet r:id="rId3" sheetId="3" name="de_escalation_evaluation"/>
-    <sheet r:id="rId4" sheetId="4" name="role_playing_evaluation"/>
+    <sheet name="synthesis_dataset" sheetId="1" r:id="rId1"/>
+    <sheet name="Data_with_negative_example" sheetId="2" r:id="rId2"/>
+    <sheet name="de_escalation_evaluation" sheetId="3" r:id="rId3"/>
+    <sheet name="role_playing_evaluation" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="131">
   <si>
     <t>Conversation_Id</t>
   </si>
@@ -1838,12 +1857,14 @@
 •	He is unarmed.
 </t>
   </si>
+  <si>
+    <t>ID</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1860,7 +1881,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1892,59 +1913,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1955,10 +1967,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -1996,71 +2008,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2088,7 +2100,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2111,11 +2123,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -2124,13 +2136,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2140,7 +2152,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -2149,7 +2161,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -2158,7 +2170,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -2166,10 +2178,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -2234,29 +2246,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="13" width="14.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="14.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="14" width="31.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="27.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="14" width="60.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="14" width="37.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="14" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="14" width="20.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="13" width="17.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="14" width="102.57642857142856" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="11" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="11" width="87.14785714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="2" width="14.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="102.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="87.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>38</v>
       </c>
@@ -2297,7 +2308,7 @@
         <v>99</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="669">
+    <row r="2" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -2336,7 +2347,7 @@
       </c>
       <c r="M2" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="282">
+    <row r="3" spans="1:13" ht="282" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -2375,7 +2386,7 @@
       </c>
       <c r="M3" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="234">
+    <row r="4" spans="1:13" ht="234" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -2412,9 +2423,8 @@
       <c r="L4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="690">
+    </row>
+    <row r="5" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -2451,9 +2461,8 @@
       <c r="L5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M5" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="618">
+    </row>
+    <row r="6" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -2490,9 +2499,8 @@
       <c r="L6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M6" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="426">
+    </row>
+    <row r="7" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -2529,9 +2537,8 @@
       <c r="L7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M7" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="474">
+    </row>
+    <row r="8" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -2568,9 +2575,8 @@
       <c r="L8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M8" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="642">
+    </row>
+    <row r="9" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -2607,9 +2613,8 @@
       <c r="L9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M9" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="330">
+    </row>
+    <row r="10" spans="1:13" ht="330" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -2646,9 +2651,8 @@
       <c r="L10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M10" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="786">
+    </row>
+    <row r="11" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -2685,9 +2689,8 @@
       <c r="L11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M11" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="690">
+    </row>
+    <row r="12" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -2724,11 +2727,10 @@
       <c r="L12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M12" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="378">
+    </row>
+    <row r="13" spans="1:13" ht="378" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
-        <f>A12+1</f>
+        <v>12</v>
       </c>
       <c r="B13" s="5">
         <v>2</v>
@@ -2763,11 +2765,10 @@
       <c r="L13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M13" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="450">
+    </row>
+    <row r="14" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
-        <f>A13+1</f>
+        <v>13</v>
       </c>
       <c r="B14" s="5">
         <v>3</v>
@@ -2802,11 +2803,10 @@
       <c r="L14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M14" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="402">
+    </row>
+    <row r="15" spans="1:13" ht="402" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
-        <f>A14+1</f>
+        <v>14</v>
       </c>
       <c r="B15" s="5">
         <v>3</v>
@@ -2841,11 +2841,10 @@
       <c r="L15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M15" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="306">
+    </row>
+    <row r="16" spans="1:13" ht="306" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
-        <f>A15+1</f>
+        <v>15</v>
       </c>
       <c r="B16" s="5">
         <v>3</v>
@@ -2880,11 +2879,10 @@
       <c r="L16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M16" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="546">
+    </row>
+    <row r="17" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
-        <f>A16+1</f>
+        <v>16</v>
       </c>
       <c r="B17" s="5">
         <v>3</v>
@@ -2919,11 +2917,10 @@
       <c r="L17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M17" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="702">
+    </row>
+    <row r="18" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
-        <f>A17+1</f>
+        <v>17</v>
       </c>
       <c r="B18" s="5">
         <v>3</v>
@@ -2958,11 +2955,10 @@
       <c r="L18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M18" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="426">
+    </row>
+    <row r="19" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
-        <f>A18+1</f>
+        <v>18</v>
       </c>
       <c r="B19" s="5">
         <v>3</v>
@@ -2997,11 +2993,10 @@
       <c r="L19" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M19" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="330">
+    </row>
+    <row r="20" spans="1:12" ht="330" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
-        <f>A19+1</f>
+        <v>19</v>
       </c>
       <c r="B20" s="5">
         <v>4</v>
@@ -3036,11 +3031,10 @@
       <c r="L20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M20" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="306">
+    </row>
+    <row r="21" spans="1:12" ht="306" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
-        <f>A20+1</f>
+        <v>20</v>
       </c>
       <c r="B21" s="5">
         <v>4</v>
@@ -3075,11 +3069,10 @@
       <c r="L21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M21" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="258">
+    </row>
+    <row r="22" spans="1:12" ht="258" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
-        <f>A21+1</f>
+        <v>21</v>
       </c>
       <c r="B22" s="5">
         <v>4</v>
@@ -3114,11 +3107,10 @@
       <c r="L22" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M22" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="546">
+    </row>
+    <row r="23" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
-        <f>A22+1</f>
+        <v>22</v>
       </c>
       <c r="B23" s="5">
         <v>4</v>
@@ -3153,11 +3145,10 @@
       <c r="L23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M23" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="498">
+    </row>
+    <row r="24" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
-        <f>A23+1</f>
+        <v>23</v>
       </c>
       <c r="B24" s="5">
         <v>4</v>
@@ -3192,11 +3183,10 @@
       <c r="L24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M24" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="426">
+    </row>
+    <row r="25" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
-        <f>A24+1</f>
+        <v>24</v>
       </c>
       <c r="B25" s="5">
         <v>4</v>
@@ -3231,11 +3221,10 @@
       <c r="L25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M25" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="402">
+    </row>
+    <row r="26" spans="1:12" ht="402" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
-        <f>A25+1</f>
+        <v>25</v>
       </c>
       <c r="B26" s="5">
         <v>5</v>
@@ -3270,11 +3259,10 @@
       <c r="L26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M26" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="306">
+    </row>
+    <row r="27" spans="1:12" ht="306" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
-        <f>A26+1</f>
+        <v>26</v>
       </c>
       <c r="B27" s="5">
         <v>5</v>
@@ -3309,11 +3297,10 @@
       <c r="L27" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M27" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="258">
+    </row>
+    <row r="28" spans="1:12" ht="258" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
-        <f>A27+1</f>
+        <v>27</v>
       </c>
       <c r="B28" s="5">
         <v>5</v>
@@ -3348,11 +3335,10 @@
       <c r="L28" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M28" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="594">
+    </row>
+    <row r="29" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
-        <f>A28+1</f>
+        <v>28</v>
       </c>
       <c r="B29" s="5">
         <v>5</v>
@@ -3387,11 +3373,10 @@
       <c r="L29" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M29" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="546">
+    </row>
+    <row r="30" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
-        <f>A29+1</f>
+        <v>29</v>
       </c>
       <c r="B30" s="5">
         <v>5</v>
@@ -3426,11 +3411,10 @@
       <c r="L30" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M30" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="426">
+    </row>
+    <row r="31" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
-        <f>A30+1</f>
+        <v>30</v>
       </c>
       <c r="B31" s="5">
         <v>5</v>
@@ -3465,12 +3449,9 @@
       <c r="L31" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M31" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="5">
-        <f>A31+1</f>
-      </c>
+    </row>
+    <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
@@ -3480,14 +3461,9 @@
       <c r="H32" s="6"/>
       <c r="I32" s="5"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="5">
-        <f>A32+1</f>
-      </c>
+    </row>
+    <row r="33" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
@@ -3497,14 +3473,9 @@
       <c r="H33" s="6"/>
       <c r="I33" s="5"/>
       <c r="J33" s="6"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="5">
-        <f>A33+1</f>
-      </c>
+    </row>
+    <row r="34" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
@@ -3514,14 +3485,9 @@
       <c r="H34" s="6"/>
       <c r="I34" s="5"/>
       <c r="J34" s="6"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="5">
-        <f>A34+1</f>
-      </c>
+    </row>
+    <row r="35" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -3531,14 +3497,9 @@
       <c r="H35" s="6"/>
       <c r="I35" s="5"/>
       <c r="J35" s="6"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="5">
-        <f>A35+1</f>
-      </c>
+    </row>
+    <row r="36" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
@@ -3548,14 +3509,9 @@
       <c r="H36" s="6"/>
       <c r="I36" s="5"/>
       <c r="J36" s="6"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="5">
-        <f>A36+1</f>
-      </c>
+    </row>
+    <row r="37" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
@@ -3565,9 +3521,6 @@
       <c r="H37" s="6"/>
       <c r="I37" s="5"/>
       <c r="J37" s="6"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3575,29 +3528,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F102"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="10" width="22.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="19.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="11" width="31.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="11" width="32.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="22.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.5" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -3610,11 +3562,11 @@
         <v>41</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="5">
+    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3626,15 +3578,15 @@
       <c r="E2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="5">
+    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -3643,18 +3595,19 @@
       <c r="D3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="7">
-        <f>F2+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="5">
+      <c r="F3" s="1">
+        <f t="shared" ref="F3:F31" si="0">F2+1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -3663,18 +3616,19 @@
       <c r="D4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="1">
         <v>1</v>
       </c>
-      <c r="F4" s="7">
-        <f>F3+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="5">
+      <c r="F4" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -3683,18 +3637,19 @@
       <c r="D5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="1">
         <v>1</v>
       </c>
-      <c r="F5" s="7">
-        <f>F4+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="5">
+      <c r="F5" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3703,18 +3658,19 @@
       <c r="D6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="7">
-        <f>F5+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="5">
+      <c r="F6" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -3723,18 +3679,19 @@
       <c r="D7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="7">
-        <f>F6+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="5">
+      <c r="F7" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -3743,18 +3700,19 @@
       <c r="D8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="7">
-        <f>F7+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="5">
+      <c r="F8" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3763,18 +3721,19 @@
       <c r="D9" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="7">
-        <f>F8+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="5">
+      <c r="F9" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3783,18 +3742,19 @@
       <c r="D10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="7">
-        <f>F9+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="5">
+      <c r="F10" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3803,18 +3763,19 @@
       <c r="D11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="7">
-        <f>F10+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="5">
+      <c r="F11" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3823,18 +3784,19 @@
       <c r="D12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="1">
         <v>1</v>
       </c>
-      <c r="F12" s="7">
-        <f>F11+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="5">
-        <f>A12+1</f>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="F12" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3843,18 +3805,19 @@
       <c r="D13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="1">
         <v>1</v>
       </c>
-      <c r="F13" s="7">
-        <f>F12+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="5">
-        <f>A13+1</f>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="F13" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3863,18 +3826,19 @@
       <c r="D14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="1">
         <v>1</v>
       </c>
-      <c r="F14" s="7">
-        <f>F13+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="5">
-        <f>A14+1</f>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="F14" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3883,18 +3847,19 @@
       <c r="D15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="1">
         <v>1</v>
       </c>
-      <c r="F15" s="7">
-        <f>F14+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="5">
-        <f>A15+1</f>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="F15" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3903,18 +3868,19 @@
       <c r="D16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="1">
         <v>1</v>
       </c>
-      <c r="F16" s="7">
-        <f>F15+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="5">
-        <f>A16+1</f>
-      </c>
-      <c r="B17" s="6" t="s">
+      <c r="F16" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3923,18 +3889,19 @@
       <c r="D17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="1">
         <v>1</v>
       </c>
-      <c r="F17" s="7">
-        <f>F16+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="5">
-        <f>A17+1</f>
-      </c>
-      <c r="B18" s="6" t="s">
+      <c r="F17" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3943,18 +3910,19 @@
       <c r="D18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="1">
         <v>1</v>
       </c>
-      <c r="F18" s="7">
-        <f>F17+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="5">
-        <f>A18+1</f>
-      </c>
-      <c r="B19" s="6" t="s">
+      <c r="F18" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3963,18 +3931,19 @@
       <c r="D19" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="1">
         <v>1</v>
       </c>
-      <c r="F19" s="7">
-        <f>F18+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="5">
-        <f>A19+1</f>
-      </c>
-      <c r="B20" s="6" t="s">
+      <c r="F19" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3983,18 +3952,19 @@
       <c r="D20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="1">
         <v>1</v>
       </c>
-      <c r="F20" s="7">
-        <f>F19+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="5">
-        <f>A20+1</f>
-      </c>
-      <c r="B21" s="6" t="s">
+      <c r="F20" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -4003,18 +3973,19 @@
       <c r="D21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="1">
         <v>1</v>
       </c>
-      <c r="F21" s="7">
-        <f>F20+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="5">
-        <f>A21+1</f>
-      </c>
-      <c r="B22" s="6" t="s">
+      <c r="F21" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -4023,18 +3994,19 @@
       <c r="D22" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="1">
         <v>1</v>
       </c>
-      <c r="F22" s="7">
-        <f>F21+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="5">
-        <f>A22+1</f>
-      </c>
-      <c r="B23" s="6" t="s">
+      <c r="F22" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -4043,18 +4015,19 @@
       <c r="D23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="1">
         <v>1</v>
       </c>
-      <c r="F23" s="7">
-        <f>F22+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="5">
-        <f>A23+1</f>
-      </c>
-      <c r="B24" s="6" t="s">
+      <c r="F23" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -4063,18 +4036,19 @@
       <c r="D24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="1">
         <v>1</v>
       </c>
-      <c r="F24" s="7">
-        <f>F23+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="5">
-        <f>A24+1</f>
-      </c>
-      <c r="B25" s="6" t="s">
+      <c r="F24" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -4083,18 +4057,19 @@
       <c r="D25" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="1">
         <v>1</v>
       </c>
-      <c r="F25" s="7">
-        <f>F24+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="5">
-        <f>A25+1</f>
-      </c>
-      <c r="B26" s="6" t="s">
+      <c r="F25" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -4103,18 +4078,19 @@
       <c r="D26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="1">
         <v>1</v>
       </c>
-      <c r="F26" s="7">
-        <f>F25+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="5">
-        <f>A26+1</f>
-      </c>
-      <c r="B27" s="6" t="s">
+      <c r="F26" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -4123,18 +4099,19 @@
       <c r="D27" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="1">
         <v>1</v>
       </c>
-      <c r="F27" s="7">
-        <f>F26+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="5">
-        <f>A27+1</f>
-      </c>
-      <c r="B28" s="6" t="s">
+      <c r="F27" s="1">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -4143,18 +4120,19 @@
       <c r="D28" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="1">
         <v>1</v>
       </c>
-      <c r="F28" s="7">
-        <f>F27+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="5">
-        <f>A28+1</f>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="F28" s="1">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -4163,18 +4141,19 @@
       <c r="D29" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="1">
         <v>1</v>
       </c>
-      <c r="F29" s="7">
-        <f>F28+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="5">
-        <f>A29+1</f>
-      </c>
-      <c r="B30" s="6" t="s">
+      <c r="F29" s="1">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -4183,18 +4162,19 @@
       <c r="D30" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="1">
         <v>1</v>
       </c>
-      <c r="F30" s="7">
-        <f>F29+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="5">
-        <f>A30+1</f>
-      </c>
-      <c r="B31" s="6" t="s">
+      <c r="F30" s="1">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -4203,18 +4183,19 @@
       <c r="D31" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="1">
         <v>1</v>
       </c>
-      <c r="F31" s="7">
-        <f>F30+1</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="5">
+      <c r="F31" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -4226,13 +4207,13 @@
       <c r="E32" s="1">
         <v>0</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="7">
-        <f>A32+1</f>
+    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>5</v>
@@ -4243,16 +4224,16 @@
       <c r="D33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E33" s="7">
-        <v>0</v>
-      </c>
-      <c r="F33" s="7">
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="7">
-        <f>A33+1</f>
+    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>5</v>
@@ -4263,16 +4244,16 @@
       <c r="D34" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="7">
-        <v>0</v>
-      </c>
-      <c r="F34" s="7">
+      <c r="E34" s="1">
+        <v>0</v>
+      </c>
+      <c r="F34" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="7">
-        <f>A34+1</f>
+    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>5</v>
@@ -4283,16 +4264,16 @@
       <c r="D35" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E35" s="7">
-        <v>0</v>
-      </c>
-      <c r="F35" s="7">
+      <c r="E35" s="1">
+        <v>0</v>
+      </c>
+      <c r="F35" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="7">
-        <f>A35+1</f>
+    <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>5</v>
@@ -4303,16 +4284,16 @@
       <c r="D36" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E36" s="7">
-        <v>0</v>
-      </c>
-      <c r="F36" s="7">
+      <c r="E36" s="1">
+        <v>0</v>
+      </c>
+      <c r="F36" s="1">
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="7">
-        <f>A36+1</f>
+    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>7</v>
@@ -4323,16 +4304,16 @@
       <c r="D37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E37" s="7">
-        <v>0</v>
-      </c>
-      <c r="F37" s="7">
+      <c r="E37" s="1">
+        <v>0</v>
+      </c>
+      <c r="F37" s="1">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="7">
-        <f>A37+1</f>
+    <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>7</v>
@@ -4343,16 +4324,16 @@
       <c r="D38" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="7">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7">
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
+      <c r="F38" s="1">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="7">
-        <f>A38+1</f>
+    <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>7</v>
@@ -4363,16 +4344,16 @@
       <c r="D39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E39" s="7">
-        <v>0</v>
-      </c>
-      <c r="F39" s="7">
+      <c r="E39" s="1">
+        <v>0</v>
+      </c>
+      <c r="F39" s="1">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="7">
-        <f>A39+1</f>
+    <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>7</v>
@@ -4383,16 +4364,16 @@
       <c r="D40" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E40" s="7">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7">
+      <c r="E40" s="1">
+        <v>0</v>
+      </c>
+      <c r="F40" s="1">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="7">
-        <f>A40+1</f>
+    <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>9</v>
@@ -4403,16 +4384,16 @@
       <c r="D41" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E41" s="7">
-        <v>0</v>
-      </c>
-      <c r="F41" s="7">
+      <c r="E41" s="1">
+        <v>0</v>
+      </c>
+      <c r="F41" s="1">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="7">
-        <f>A41+1</f>
+    <row r="42" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>9</v>
@@ -4423,16 +4404,16 @@
       <c r="D42" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E42" s="7">
-        <v>0</v>
-      </c>
-      <c r="F42" s="7">
+      <c r="E42" s="1">
+        <v>0</v>
+      </c>
+      <c r="F42" s="1">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="7">
-        <f>A42+1</f>
+    <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>9</v>
@@ -4443,16 +4424,16 @@
       <c r="D43" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E43" s="7">
-        <v>0</v>
-      </c>
-      <c r="F43" s="7">
+      <c r="E43" s="1">
+        <v>0</v>
+      </c>
+      <c r="F43" s="1">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="7">
-        <f>A43+1</f>
+    <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>5</v>
@@ -4463,16 +4444,16 @@
       <c r="D44" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E44" s="7">
-        <v>0</v>
-      </c>
-      <c r="F44" s="7">
+      <c r="E44" s="1">
+        <v>0</v>
+      </c>
+      <c r="F44" s="1">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="7">
-        <f>A44+1</f>
+    <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>5</v>
@@ -4483,16 +4464,16 @@
       <c r="D45" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E45" s="7">
-        <v>0</v>
-      </c>
-      <c r="F45" s="7">
+      <c r="E45" s="1">
+        <v>0</v>
+      </c>
+      <c r="F45" s="1">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="7">
-        <f>A45+1</f>
+    <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>5</v>
@@ -4503,16 +4484,16 @@
       <c r="D46" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E46" s="7">
-        <v>0</v>
-      </c>
-      <c r="F46" s="7">
+      <c r="E46" s="1">
+        <v>0</v>
+      </c>
+      <c r="F46" s="1">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="7">
-        <f>A46+1</f>
+    <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>7</v>
@@ -4523,16 +4504,16 @@
       <c r="D47" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E47" s="7">
-        <v>0</v>
-      </c>
-      <c r="F47" s="7">
+      <c r="E47" s="1">
+        <v>0</v>
+      </c>
+      <c r="F47" s="1">
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="7">
-        <f>A47+1</f>
+    <row r="48" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>7</v>
@@ -4543,16 +4524,16 @@
       <c r="D48" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E48" s="7">
-        <v>0</v>
-      </c>
-      <c r="F48" s="7">
+      <c r="E48" s="1">
+        <v>0</v>
+      </c>
+      <c r="F48" s="1">
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="7">
-        <f>A48+1</f>
+    <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>7</v>
@@ -4563,16 +4544,16 @@
       <c r="D49" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E49" s="7">
-        <v>0</v>
-      </c>
-      <c r="F49" s="7">
+      <c r="E49" s="1">
+        <v>0</v>
+      </c>
+      <c r="F49" s="1">
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="7">
-        <f>A49+1</f>
+    <row r="50" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>9</v>
@@ -4583,16 +4564,16 @@
       <c r="D50" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E50" s="7">
-        <v>0</v>
-      </c>
-      <c r="F50" s="7">
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
+      <c r="F50" s="1">
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
-      <c r="A51" s="7">
-        <f>A50+1</f>
+    <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>9</v>
@@ -4603,16 +4584,16 @@
       <c r="D51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E51" s="7">
-        <v>0</v>
-      </c>
-      <c r="F51" s="7">
+      <c r="E51" s="1">
+        <v>0</v>
+      </c>
+      <c r="F51" s="1">
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
-      <c r="A52" s="7">
-        <f>A51+1</f>
+    <row r="52" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>9</v>
@@ -4623,16 +4604,16 @@
       <c r="D52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E52" s="7">
-        <v>0</v>
-      </c>
-      <c r="F52" s="7">
+      <c r="E52" s="1">
+        <v>0</v>
+      </c>
+      <c r="F52" s="1">
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
-      <c r="A53" s="7">
-        <f>A52+1</f>
+    <row r="53" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>5</v>
@@ -4643,16 +4624,16 @@
       <c r="D53" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E53" s="7">
-        <v>0</v>
-      </c>
-      <c r="F53" s="7">
+      <c r="E53" s="1">
+        <v>0</v>
+      </c>
+      <c r="F53" s="1">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
-      <c r="A54" s="7">
-        <f>A53+1</f>
+    <row r="54" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>5</v>
@@ -4663,16 +4644,16 @@
       <c r="D54" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E54" s="7">
-        <v>0</v>
-      </c>
-      <c r="F54" s="7">
+      <c r="E54" s="1">
+        <v>0</v>
+      </c>
+      <c r="F54" s="1">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
-      <c r="A55" s="7">
-        <f>A54+1</f>
+    <row r="55" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>5</v>
@@ -4683,16 +4664,16 @@
       <c r="D55" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E55" s="7">
-        <v>0</v>
-      </c>
-      <c r="F55" s="7">
+      <c r="E55" s="1">
+        <v>0</v>
+      </c>
+      <c r="F55" s="1">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
-      <c r="A56" s="7">
-        <f>A55+1</f>
+    <row r="56" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>5</v>
@@ -4703,16 +4684,16 @@
       <c r="D56" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E56" s="7">
-        <v>0</v>
-      </c>
-      <c r="F56" s="7">
+      <c r="E56" s="1">
+        <v>0</v>
+      </c>
+      <c r="F56" s="1">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
-      <c r="A57" s="7">
-        <f>A56+1</f>
+    <row r="57" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>5</v>
@@ -4723,16 +4704,16 @@
       <c r="D57" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E57" s="7">
-        <v>0</v>
-      </c>
-      <c r="F57" s="7">
+      <c r="E57" s="1">
+        <v>0</v>
+      </c>
+      <c r="F57" s="1">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
-      <c r="A58" s="7">
-        <f>A57+1</f>
+    <row r="58" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>7</v>
@@ -4743,16 +4724,16 @@
       <c r="D58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E58" s="7">
-        <v>0</v>
-      </c>
-      <c r="F58" s="7">
+      <c r="E58" s="1">
+        <v>0</v>
+      </c>
+      <c r="F58" s="1">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
-      <c r="A59" s="7">
-        <f>A58+1</f>
+    <row r="59" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>7</v>
@@ -4763,16 +4744,16 @@
       <c r="D59" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E59" s="7">
-        <v>0</v>
-      </c>
-      <c r="F59" s="7">
+      <c r="E59" s="1">
+        <v>0</v>
+      </c>
+      <c r="F59" s="1">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
-      <c r="A60" s="7">
-        <f>A59+1</f>
+    <row r="60" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>7</v>
@@ -4783,16 +4764,16 @@
       <c r="D60" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E60" s="7">
-        <v>0</v>
-      </c>
-      <c r="F60" s="7">
+      <c r="E60" s="1">
+        <v>0</v>
+      </c>
+      <c r="F60" s="1">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
-      <c r="A61" s="7">
-        <f>A60+1</f>
+    <row r="61" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>9</v>
@@ -4803,16 +4784,16 @@
       <c r="D61" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E61" s="7">
-        <v>0</v>
-      </c>
-      <c r="F61" s="7">
+      <c r="E61" s="1">
+        <v>0</v>
+      </c>
+      <c r="F61" s="1">
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
-      <c r="A62" s="7">
-        <f>A61+1</f>
+    <row r="62" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>9</v>
@@ -4823,16 +4804,16 @@
       <c r="D62" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E62" s="7">
-        <v>0</v>
-      </c>
-      <c r="F62" s="7">
+      <c r="E62" s="1">
+        <v>0</v>
+      </c>
+      <c r="F62" s="1">
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
-      <c r="A63" s="7">
-        <f>A62+1</f>
+    <row r="63" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>9</v>
@@ -4843,16 +4824,16 @@
       <c r="D63" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E63" s="7">
-        <v>0</v>
-      </c>
-      <c r="F63" s="7">
+      <c r="E63" s="1">
+        <v>0</v>
+      </c>
+      <c r="F63" s="1">
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
-      <c r="A64" s="7">
-        <f>A63+1</f>
+    <row r="64" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>5</v>
@@ -4863,16 +4844,16 @@
       <c r="D64" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E64" s="7">
-        <v>0</v>
-      </c>
-      <c r="F64" s="7">
+      <c r="E64" s="1">
+        <v>0</v>
+      </c>
+      <c r="F64" s="1">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
-      <c r="A65" s="7">
-        <f>A64+1</f>
+    <row r="65" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>5</v>
@@ -4883,16 +4864,16 @@
       <c r="D65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E65" s="7">
-        <v>0</v>
-      </c>
-      <c r="F65" s="7">
+      <c r="E65" s="1">
+        <v>0</v>
+      </c>
+      <c r="F65" s="1">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
-      <c r="A66" s="7">
-        <f>A65+1</f>
+    <row r="66" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>5</v>
@@ -4903,16 +4884,16 @@
       <c r="D66" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E66" s="7">
-        <v>0</v>
-      </c>
-      <c r="F66" s="7">
+      <c r="E66" s="1">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
-      <c r="A67" s="7">
-        <f>A66+1</f>
+    <row r="67" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>7</v>
@@ -4923,16 +4904,16 @@
       <c r="D67" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E67" s="7">
-        <v>0</v>
-      </c>
-      <c r="F67" s="7">
+      <c r="E67" s="1">
+        <v>0</v>
+      </c>
+      <c r="F67" s="1">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
-      <c r="A68" s="7">
-        <f>A67+1</f>
+    <row r="68" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>7</v>
@@ -4943,16 +4924,16 @@
       <c r="D68" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E68" s="7">
-        <v>0</v>
-      </c>
-      <c r="F68" s="7">
+      <c r="E68" s="1">
+        <v>0</v>
+      </c>
+      <c r="F68" s="1">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
-      <c r="A69" s="7">
-        <f>A68+1</f>
+    <row r="69" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>7</v>
@@ -4963,16 +4944,16 @@
       <c r="D69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E69" s="7">
-        <v>0</v>
-      </c>
-      <c r="F69" s="7">
+      <c r="E69" s="1">
+        <v>0</v>
+      </c>
+      <c r="F69" s="1">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
-      <c r="A70" s="7">
-        <f>A69+1</f>
+    <row r="70" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>7</v>
@@ -4983,16 +4964,16 @@
       <c r="D70" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E70" s="7">
-        <v>0</v>
-      </c>
-      <c r="F70" s="7">
+      <c r="E70" s="1">
+        <v>0</v>
+      </c>
+      <c r="F70" s="1">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
-      <c r="A71" s="7">
-        <f>A70+1</f>
+    <row r="71" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>7</v>
@@ -5003,16 +4984,16 @@
       <c r="D71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E71" s="7">
-        <v>0</v>
-      </c>
-      <c r="F71" s="7">
+      <c r="E71" s="1">
+        <v>0</v>
+      </c>
+      <c r="F71" s="1">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
-      <c r="A72" s="7">
-        <f>A71+1</f>
+    <row r="72" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>9</v>
@@ -5023,16 +5004,16 @@
       <c r="D72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E72" s="7">
-        <v>0</v>
-      </c>
-      <c r="F72" s="7">
+      <c r="E72" s="1">
+        <v>0</v>
+      </c>
+      <c r="F72" s="1">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
-      <c r="A73" s="7">
-        <f>A72+1</f>
+    <row r="73" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>9</v>
@@ -5043,16 +5024,16 @@
       <c r="D73" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E73" s="7">
-        <v>0</v>
-      </c>
-      <c r="F73" s="7">
+      <c r="E73" s="1">
+        <v>0</v>
+      </c>
+      <c r="F73" s="1">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
-      <c r="A74" s="7">
-        <f>A73+1</f>
+    <row r="74" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>9</v>
@@ -5063,336 +5044,342 @@
       <c r="D74" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E74" s="7">
-        <v>0</v>
-      </c>
-      <c r="F74" s="7">
+      <c r="E74" s="1">
+        <v>0</v>
+      </c>
+      <c r="F74" s="1">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
-      <c r="A75" s="7">
-        <f>A74+1</f>
-      </c>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="7">
-        <v>0</v>
-      </c>
-      <c r="F75" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
-      <c r="A76" s="7">
-        <f>A75+1</f>
-      </c>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="7">
-        <v>0</v>
-      </c>
-      <c r="F76" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
-      <c r="A77" s="7">
-        <f>A76+1</f>
-      </c>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="7">
-        <v>0</v>
-      </c>
-      <c r="F77" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
-      <c r="A78" s="7">
-        <f>A77+1</f>
-      </c>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="7">
-        <v>0</v>
-      </c>
-      <c r="F78" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
-      <c r="A79" s="7">
-        <f>A78+1</f>
-      </c>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="7">
-        <v>0</v>
-      </c>
-      <c r="F79" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
-      <c r="A80" s="7">
-        <f>A79+1</f>
-      </c>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="7">
-        <v>0</v>
-      </c>
-      <c r="F80" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
-      <c r="A81" s="7">
-        <f>A80+1</f>
-      </c>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="7">
-        <v>0</v>
-      </c>
-      <c r="F81" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
-      <c r="A82" s="7">
-        <f>A81+1</f>
-      </c>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="7">
-        <v>0</v>
-      </c>
-      <c r="F82" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
-      <c r="A83" s="7">
-        <f>A82+1</f>
-      </c>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="7">
-        <v>0</v>
-      </c>
-      <c r="F83" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
-      <c r="A84" s="7">
-        <f>A83+1</f>
-      </c>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="7">
-        <v>0</v>
-      </c>
-      <c r="F84" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
-      <c r="A85" s="7">
-        <f>A84+1</f>
-      </c>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="7">
-        <v>0</v>
-      </c>
-      <c r="F85" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
-      <c r="A86" s="7">
-        <f>A85+1</f>
-      </c>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="7">
-        <v>0</v>
-      </c>
-      <c r="F86" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
-      <c r="A87" s="7">
-        <f>A86+1</f>
-      </c>
-      <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="7">
-        <v>0</v>
-      </c>
-      <c r="F87" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
-      <c r="A88" s="7">
-        <f>A87+1</f>
-      </c>
-      <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="7">
-        <v>0</v>
-      </c>
-      <c r="F88" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
-      <c r="A89" s="7">
-        <f>A88+1</f>
-      </c>
-      <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="7">
-        <v>0</v>
-      </c>
-      <c r="F89" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
-      <c r="A90" s="7">
-        <f>A89+1</f>
-      </c>
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="7">
-        <v>0</v>
-      </c>
-      <c r="F90" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
-      <c r="A91" s="7">
-        <f>A90+1</f>
-      </c>
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="7">
-        <v>0</v>
-      </c>
-      <c r="F91" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
-      <c r="A92" s="7">
-        <f>A91+1</f>
-      </c>
-      <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="7">
-        <v>0</v>
-      </c>
-      <c r="F92" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
-      <c r="A93" s="7">
-        <f>A92+1</f>
-      </c>
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="7">
-        <v>0</v>
-      </c>
-      <c r="F93" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
-      <c r="A94" s="7">
-        <f>A93+1</f>
-      </c>
-      <c r="B94" s="8"/>
-      <c r="C94" s="8"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="7">
-        <v>0</v>
-      </c>
-      <c r="F94" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
-      <c r="A95" s="7">
-        <f>A94+1</f>
-      </c>
-      <c r="B95" s="8"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
-      <c r="E95" s="7">
-        <v>0</v>
-      </c>
-      <c r="F95" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
-      <c r="A96" s="7">
-        <f>A95+1</f>
-      </c>
-      <c r="B96" s="8"/>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="7">
-        <v>0</v>
-      </c>
-      <c r="F96" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
-      <c r="A97" s="7">
-        <f>A96+1</f>
-      </c>
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="7">
-        <v>0</v>
-      </c>
-      <c r="F97" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
-      <c r="A98" s="7">
-        <f>A97+1</f>
-      </c>
-      <c r="B98" s="8"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="7">
-        <v>0</v>
-      </c>
-      <c r="F98" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
-      <c r="A99" s="7">
-        <f>A98+1</f>
-      </c>
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="7">
-        <v>0</v>
-      </c>
-      <c r="F99" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
-      <c r="A100" s="7">
-        <f>A99+1</f>
-      </c>
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="7">
-        <v>0</v>
-      </c>
-      <c r="F100" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
-      <c r="A101" s="7">
-        <f>A100+1</f>
-      </c>
-      <c r="B101" s="8"/>
-      <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="7">
-        <v>0</v>
-      </c>
-      <c r="F101" s="9"/>
+    <row r="75" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="1">
+        <v>0</v>
+      </c>
+      <c r="F75" s="10"/>
+    </row>
+    <row r="76" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="1">
+        <v>0</v>
+      </c>
+      <c r="F76" s="10"/>
+    </row>
+    <row r="77" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="1">
+        <v>0</v>
+      </c>
+      <c r="F77" s="10"/>
+    </row>
+    <row r="78" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="1">
+        <v>0</v>
+      </c>
+      <c r="F78" s="10"/>
+    </row>
+    <row r="79" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="1">
+        <v>0</v>
+      </c>
+      <c r="F79" s="10"/>
+    </row>
+    <row r="80" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="1">
+        <v>0</v>
+      </c>
+      <c r="F80" s="10"/>
+    </row>
+    <row r="81" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="1">
+        <v>0</v>
+      </c>
+      <c r="F81" s="10"/>
+    </row>
+    <row r="82" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="1">
+        <v>0</v>
+      </c>
+      <c r="F82" s="10"/>
+    </row>
+    <row r="83" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="1">
+        <v>0</v>
+      </c>
+      <c r="F83" s="10"/>
+    </row>
+    <row r="84" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="1">
+        <v>0</v>
+      </c>
+      <c r="F84" s="10"/>
+    </row>
+    <row r="85" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="1">
+        <v>0</v>
+      </c>
+      <c r="F85" s="10"/>
+    </row>
+    <row r="86" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="1">
+        <v>0</v>
+      </c>
+      <c r="F86" s="10"/>
+    </row>
+    <row r="87" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="1">
+        <v>0</v>
+      </c>
+      <c r="F87" s="10"/>
+    </row>
+    <row r="88" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="1">
+        <v>0</v>
+      </c>
+      <c r="F88" s="10"/>
+    </row>
+    <row r="89" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="4"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="1">
+        <v>0</v>
+      </c>
+      <c r="F89" s="10"/>
+    </row>
+    <row r="90" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="1">
+        <v>0</v>
+      </c>
+      <c r="F90" s="10"/>
+    </row>
+    <row r="91" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="1">
+        <v>0</v>
+      </c>
+      <c r="F91" s="10"/>
+    </row>
+    <row r="92" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="1">
+        <v>0</v>
+      </c>
+      <c r="F92" s="10"/>
+    </row>
+    <row r="93" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="1">
+        <v>0</v>
+      </c>
+      <c r="F93" s="10"/>
+    </row>
+    <row r="94" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="1">
+        <v>0</v>
+      </c>
+      <c r="F94" s="10"/>
+    </row>
+    <row r="95" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="1">
+        <v>0</v>
+      </c>
+      <c r="F95" s="10"/>
+    </row>
+    <row r="96" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="1">
+        <v>0</v>
+      </c>
+      <c r="F96" s="10"/>
+    </row>
+    <row r="97" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="1">
+        <v>0</v>
+      </c>
+      <c r="F97" s="10"/>
+    </row>
+    <row r="98" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="1">
+        <v>0</v>
+      </c>
+      <c r="F98" s="10"/>
+    </row>
+    <row r="99" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="1">
+        <v>0</v>
+      </c>
+      <c r="F99" s="10"/>
+    </row>
+    <row r="100" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="1">
+        <v>0</v>
+      </c>
+      <c r="F100" s="10"/>
+    </row>
+    <row r="101" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="1">
+        <v>0</v>
+      </c>
+      <c r="F101" s="10"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
+        <f t="shared" ref="A66:A102" si="1">A101+1</f>
+        <v>101</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5400,27 +5387,22 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="53.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="3" width="46.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="13.5" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5443,7 +5425,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -5466,7 +5448,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -5489,7 +5471,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -5512,7 +5494,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -5535,7 +5517,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -5558,7 +5540,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -5581,7 +5563,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -5604,7 +5586,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -5627,7 +5609,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -5650,7 +5632,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -5673,7 +5655,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row r="12" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -5696,9 +5678,10 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row r="13" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <f>A12+1</f>
+        <f t="shared" ref="A13:A31" si="0">A12+1</f>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>9</v>
@@ -5719,9 +5702,10 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row r="14" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <f>A13+1</f>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -5742,9 +5726,10 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row r="15" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <f>A14+1</f>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>7</v>
@@ -5765,9 +5750,10 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row r="16" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <f>A15+1</f>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>9</v>
@@ -5788,9 +5774,10 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row r="17" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <f>A16+1</f>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
@@ -5811,9 +5798,10 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row r="18" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <f>A17+1</f>
+        <f t="shared" si="0"/>
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
@@ -5834,9 +5822,10 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row r="19" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <f>A18+1</f>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>9</v>
@@ -5857,9 +5846,10 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row r="20" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <f>A19+1</f>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>5</v>
@@ -5880,9 +5870,10 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row r="21" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <f>A20+1</f>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>7</v>
@@ -5903,9 +5894,10 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row r="22" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <f>A21+1</f>
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>9</v>
@@ -5926,9 +5918,10 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row r="23" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <f>A22+1</f>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>5</v>
@@ -5949,9 +5942,10 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row r="24" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <f>A23+1</f>
+        <f t="shared" si="0"/>
+        <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>7</v>
@@ -5972,9 +5966,10 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row r="25" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <f>A24+1</f>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>9</v>
@@ -5995,9 +5990,10 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row r="26" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <f>A25+1</f>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>5</v>
@@ -6018,9 +6014,10 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row r="27" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <f>A26+1</f>
+        <f t="shared" si="0"/>
+        <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>7</v>
@@ -6041,9 +6038,10 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row r="28" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <f>A27+1</f>
+        <f t="shared" si="0"/>
+        <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>9</v>
@@ -6064,9 +6062,10 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row r="29" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <f>A28+1</f>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>5</v>
@@ -6087,9 +6086,10 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row r="30" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <f>A29+1</f>
+        <f t="shared" si="0"/>
+        <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>7</v>
@@ -6110,9 +6110,10 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row r="31" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <f>A30+1</f>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>9</v>
@@ -6139,12 +6140,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/de-escalation training dataset.xlsx
+++ b/data/de-escalation training dataset.xlsx
@@ -1,42 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10830"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mdhasebulhasan/Documents/Research/de-escaltion/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B889595D-1478-CE49-9819-A8D70B26B9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="synthesis_dataset" sheetId="1" r:id="rId1"/>
-    <sheet name="Data_with_negative_example" sheetId="2" r:id="rId2"/>
-    <sheet name="de_escalation_evaluation" sheetId="3" r:id="rId3"/>
-    <sheet name="role_playing_evaluation" sheetId="4" r:id="rId4"/>
+    <sheet r:id="rId1" sheetId="1" name="synthesis_dataset"/>
+    <sheet r:id="rId2" sheetId="2" name="Data_with_negative_example"/>
+    <sheet r:id="rId3" sheetId="3" name="de_escalation_evaluation"/>
+    <sheet r:id="rId4" sheetId="4" name="role_playing_evaluation"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="133">
   <si>
     <t>Conversation_Id</t>
   </si>
@@ -709,7 +690,7 @@
 William: No, I’m done being stupid. I’m finished. Goodbye.</t>
   </si>
   <si>
-    <t>id</t>
+    <t>ID</t>
   </si>
   <si>
     <t>conversation_generator</t>
@@ -728,6 +709,46 @@
   </si>
   <si>
     <t>gemeni 2.5 Flash</t>
+  </si>
+  <si>
+    <t>Jacob: Leave me the fuck alone! Get away from me!
+Officer: Sir, you need to calm down. People are starting to get concerned, and we just want to make sure you're okay.
+Jacob: I don't care! I'm not okay! I want my mom! Where is she?
+Officer: We can help you find her, but you have to stop yelling and listen to me.
+Jacob: No! You listen to me! I'm not a fucking animal! You need to back the fuck up!
+Officer: Listen to me, sir. I'm trying to help you, but you need to get yourself under control.
+Jacob: I'm not under control? I'm not under control? What the fuck do you know about it? I'm not some crazy person! Just leave me alone, you fucking piece of shit!
+Officer: That's enough. You need to stop with the language. I'm not going to tell you again.
+Jacob: You're not going to tell me again? What are you going to do, arrest me for being scared? Fuck you! Get away from me before I do something stupid!
+Officer: You are going to stop right now. Do not take another step, or I will have to use force to restrain you.
+Jacob: I'm going to do what I want! I'm going to find my mom! You can't stop me!
+Officer: Sir, I said stop! Don't make me do this!
+Jacob: I told you to back the fuck up! Get away from me!</t>
+  </si>
+  <si>
+    <t>Officer: Hey there, buddy, I’m Officer Lee. You’re looking for your mom, right?
+Jacob: Where’s Mom? Where’s Mom? I can’t find her. I lost Mom!
+Officer: I hear you. That’s really scary, not knowing where she is. We’ll find her together, I promise. Can you tell me your name so I can help?
+Jacob: Jacob! I’m Jacob! Where’s Mom?
+Officer: Thanks, Jacob. That helps a lot. I’m gonna stay right here with you until we get her, okay? You’re not alone in this.
+Jacob: My arms won’t stop. They keep hitting. Everyone’s laughing!
+Officer: You’re doing your best, Jacob. Don’t worry about them, I’m just paying attention to you. Can I sit here on the floor with you so it’s not so loud and tall?
+Jacob: Yeah… okay.
+Officer: Alright, I’m sitting down. Feels a little calmer down here, doesn’t it?
+Jacob: Yeah. But I still can’t find her.
+Officer: We’ll find her. I heard she was at the Dino-Dig exhibit earlier. Do you like dinosaurs, Jacob?
+Jacob: Dinosaurs are awesome. Do you know the T-Rex had the strongest bite force ever? Stronger than any shark.
+Officer: That’s incredible, I didn’t know it was stronger than a shark. You know so much about them. Which one’s your favorite?
+Jacob: Spinosaurus. It had a sail on its back. People think it hunted in the water like a crocodile.
+Officer: Wow, that sounds amazing. I’d love to see that. While you tell me more about it, some of my friends here are going to help look for your mom. Is it okay if we keep talking while they do?
+Jacob: Yeah. I wanna tell you about the claws.
+Officer: I’m listening. I want to hear all about those claws. You’re keeping me learning while we wait for your mom.
+Jacob: Okay. Spinosaurus claws were huge, like knives, bigger than your hand.
+Officer: That sounds powerful. Thanks for teaching me that, Jacob. Hey, I just got word—they found your mom. She’s right outside the Dino-Dig. Would you like me to walk with you to her?
+Jacob: Yes. Please, yes!
+Officer: Great. Let’s stand up together, nice and easy, and we’ll go straight to her. You did an amazing job waiting and talking with me.
+Jacob: Okay. I’m ready.
+Officer: Perfect. Let’s go see your mom. She’ll be so happy to see you.</t>
   </si>
   <si>
     <t>gemeni 2.5 - Flash</t>
@@ -1649,6 +1670,9 @@
 Jenny: Perfect. Or not.</t>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
     <t>Scenario_Number</t>
   </si>
   <si>
@@ -1857,15 +1881,13 @@
 •	He is unarmed.
 </t>
   </si>
-  <si>
-    <t>ID</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1877,6 +1899,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -1913,50 +1941,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="16">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1967,10 +2007,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -2008,71 +2048,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2100,7 +2140,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -2123,11 +2163,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -2136,13 +2176,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2152,7 +2192,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -2161,7 +2201,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -2170,7 +2210,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -2178,10 +2218,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -2246,1281 +2286,1328 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:M37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="14.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="60.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="102.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="87.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="14" width="14.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="14.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="31.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="27.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="60.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="15" width="37.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="15" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="15" width="20.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="14" width="17.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="15" width="102.57642857142856" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="10" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="10" width="87.14785714285713" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D1" s="6" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="B1" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="C1" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="D1" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="E1" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="13" t="s">
         <v>3</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>39</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
+        <v>102</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="409.6000000000001">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="12">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F2" s="6" t="s">
+      <c r="C2" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="D2" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="E2" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="12">
         <v>100</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>42</v>
       </c>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="282" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="282">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="12">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="C3" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="D3" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="E3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="12">
         <v>-20</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>42</v>
       </c>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="1:13" ht="234" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="234">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="12">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="C4" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="D4" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="E4" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="12">
         <v>-100</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
+      <c r="M4" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="409.6000000000001">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="12">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="C5" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="D5" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="E5" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="12">
         <v>100</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
+      <c r="M5" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="409.6000000000001">
+      <c r="A6" s="12">
         <v>5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="12">
         <v>1</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="C6" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="D6" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="E6" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="12">
         <v>30</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
+      <c r="M6" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="409.6000000000001">
+      <c r="A7" s="12">
         <v>6</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="12">
         <v>1</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="C7" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="D7" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="G7" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="H7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="12">
         <v>-100</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
+      <c r="M7" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="409.6000000000001">
+      <c r="A8" s="12">
         <v>7</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="12">
         <v>2</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8" s="6" t="s">
+      <c r="C8" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="D8" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="E8" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H8" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="12">
         <v>100</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
+      <c r="M8" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="409.6000000000001">
+      <c r="A9" s="12">
         <v>8</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="12">
         <v>2</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="C9" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H9" s="6" t="s">
+      <c r="F9" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="12">
         <v>-10</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="330" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="5">
+      <c r="M9" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="330">
+      <c r="A10" s="12">
         <v>9</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="12">
         <v>2</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="C10" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H10" s="6" t="s">
+      <c r="F10" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H10" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="12">
         <v>-100</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="5">
+      <c r="M10" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="409.6000000000001">
+      <c r="A11" s="12">
         <v>10</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="12">
         <v>2</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="C11" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H11" s="6" t="s">
+      <c r="F11" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="12">
         <v>100</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="5">
+      <c r="M11" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="409.6000000000001">
+      <c r="A12" s="12">
         <v>11</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="12">
         <v>2</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" s="6" t="s">
+      <c r="C12" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H12" s="6" t="s">
+      <c r="F12" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H12" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="12">
         <v>10</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="378" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="5">
+      <c r="M12" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="378">
+      <c r="A13" s="12">
         <v>12</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="12">
         <v>2</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="6" t="s">
+      <c r="C13" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H13" s="6" t="s">
+      <c r="F13" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H13" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="12">
         <v>-100</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="5">
+      <c r="M13" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="409.6000000000001">
+      <c r="A14" s="12">
         <v>13</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="12">
         <v>3</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F14" s="6" t="s">
+      <c r="C14" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="D14" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="E14" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="12">
         <v>100</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="402" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5">
+      <c r="M14" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="402">
+      <c r="A15" s="12">
         <v>14</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="12">
         <v>3</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F15" s="6" t="s">
+      <c r="C15" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="D15" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="E15" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H15" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="12">
         <v>10</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="306" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="5">
+      <c r="M15" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="306">
+      <c r="A16" s="12">
         <v>15</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="12">
         <v>3</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F16" s="6" t="s">
+      <c r="C16" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="D16" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="E16" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="12">
         <v>-100</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="5">
+      <c r="M16" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="409.6000000000001">
+      <c r="A17" s="12">
         <v>16</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="12">
         <v>3</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="C17" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="D17" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="E17" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H17" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="12">
         <v>100</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="5">
+      <c r="M17" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="409.6000000000001">
+      <c r="A18" s="12">
         <v>17</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="12">
         <v>3</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F18" s="6" t="s">
+      <c r="C18" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="D18" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="E18" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="12">
         <v>20</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="5">
+      <c r="M18" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="409.6000000000001">
+      <c r="A19" s="12">
         <v>18</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="12">
         <v>3</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F19" s="6" t="s">
+      <c r="C19" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="D19" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="E19" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="12">
         <v>-100</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="330" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="5">
+      <c r="M19" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="330">
+      <c r="A20" s="12">
         <v>19</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="12">
         <v>4</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>119</v>
+      <c r="C20" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="G20" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="E20" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="12">
         <v>100</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="306" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="5">
+        <v>47</v>
+      </c>
+      <c r="M20" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="306">
+      <c r="A21" s="12">
         <v>20</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="12">
         <v>4</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>119</v>
+      <c r="C21" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="G21" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="E21" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="H21" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="12">
         <v>20</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="258" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="5">
+        <v>47</v>
+      </c>
+      <c r="M21" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="258">
+      <c r="A22" s="12">
         <v>21</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="12">
         <v>4</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>119</v>
+      <c r="C22" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="G22" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="E22" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="H22" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="12">
         <v>-100</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="5">
+        <v>47</v>
+      </c>
+      <c r="M22" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="409.6000000000001">
+      <c r="A23" s="12">
         <v>22</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="12">
         <v>4</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>119</v>
+      <c r="C23" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="G23" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="E23" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="H23" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="12">
         <v>100</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="5">
+        <v>48</v>
+      </c>
+      <c r="M23" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="409.6000000000001">
+      <c r="A24" s="12">
         <v>23</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="12">
         <v>4</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>119</v>
+      <c r="C24" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="G24" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="E24" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="H24" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="12">
         <v>30</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>30</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="5">
+        <v>48</v>
+      </c>
+      <c r="M24" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="409.6000000000001">
+      <c r="A25" s="12">
         <v>24</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="12">
         <v>4</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>119</v>
+      <c r="C25" s="13" t="s">
+        <v>122</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="G25" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="E25" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="H25" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="12">
         <v>-100</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="402" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="5">
+        <v>48</v>
+      </c>
+      <c r="M25" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="402">
+      <c r="A26" s="12">
         <v>25</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="12">
         <v>5</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F26" s="6" t="s">
+      <c r="C26" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="D26" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="E26" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H26" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="12">
         <v>100</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="306" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="5">
+        <v>47</v>
+      </c>
+      <c r="M26" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="306">
+      <c r="A27" s="12">
         <v>26</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="12">
         <v>5</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D27" s="6" t="s">
+      <c r="C27" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H27" s="6" t="s">
+      <c r="F27" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H27" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="12">
         <v>20</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="258" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="5">
+        <v>47</v>
+      </c>
+      <c r="M27" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="258">
+      <c r="A28" s="12">
         <v>27</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="12">
         <v>5</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" s="6" t="s">
+      <c r="C28" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E28" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H28" s="6" t="s">
+      <c r="F28" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H28" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="12">
         <v>-100</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="5">
+        <v>47</v>
+      </c>
+      <c r="M28" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="409.6000000000001">
+      <c r="A29" s="12">
         <v>28</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="12">
         <v>5</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D29" s="6" t="s">
+      <c r="C29" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H29" s="6" t="s">
+      <c r="F29" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H29" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I29" s="5">
+      <c r="I29" s="12">
         <v>100</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="5">
+        <v>48</v>
+      </c>
+      <c r="M29" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="409.6000000000001">
+      <c r="A30" s="12">
         <v>29</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="12">
         <v>5</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D30" s="6" t="s">
+      <c r="C30" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H30" s="6" t="s">
+      <c r="F30" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H30" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="12">
         <v>20</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>36</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="5">
+        <v>48</v>
+      </c>
+      <c r="M30" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="409.6000000000001">
+      <c r="A31" s="12">
         <v>30</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="12">
         <v>5</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D31" s="6" t="s">
+      <c r="C31" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H31" s="6" t="s">
+      <c r="F31" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H31" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="12">
         <v>-100</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>37</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="5"/>
+        <v>48</v>
+      </c>
+      <c r="M31" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="12"/>
       <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="6"/>
-    </row>
-    <row r="34" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="6"/>
-    </row>
-    <row r="35" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="6"/>
-    </row>
-    <row r="36" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="6"/>
-    </row>
-    <row r="37" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="6"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+      <c r="A37" s="12"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3528,23 +3615,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F102"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="3" width="22.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="19.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="31.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="32.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -3562,8 +3650,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="656.25">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -3582,7 +3670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="299.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -3599,11 +3687,10 @@
         <v>1</v>
       </c>
       <c r="F3" s="1">
-        <f t="shared" ref="F3:F31" si="0">F2+1</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F2+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="248.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3620,11 +3707,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F3+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="732.75">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -3641,11 +3727,10 @@
         <v>1</v>
       </c>
       <c r="F5" s="1">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F4+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="656.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -3662,11 +3747,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F5+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="452.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -3683,11 +3767,10 @@
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F6+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="503.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -3704,11 +3787,10 @@
         <v>1</v>
       </c>
       <c r="F8" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F7+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="681.75">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -3725,11 +3807,10 @@
         <v>1</v>
       </c>
       <c r="F9" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F8+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="350.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -3746,11 +3827,10 @@
         <v>1</v>
       </c>
       <c r="F10" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F9+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="834.75">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -3767,11 +3847,10 @@
         <v>1</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F10+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="732.75">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -3788,11 +3867,10 @@
         <v>1</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F11+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="401.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -3809,11 +3887,10 @@
         <v>1</v>
       </c>
       <c r="F13" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F12+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="477.75">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -3830,11 +3907,10 @@
         <v>1</v>
       </c>
       <c r="F14" s="1">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F13+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="426.75">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -3851,11 +3927,10 @@
         <v>1</v>
       </c>
       <c r="F15" s="1">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F14+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -3863,7 +3938,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>44</v>
@@ -3872,11 +3947,10 @@
         <v>1</v>
       </c>
       <c r="F16" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F15+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -3884,7 +3958,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>43</v>
@@ -3893,11 +3967,10 @@
         <v>1</v>
       </c>
       <c r="F17" s="1">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F16+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -3914,11 +3987,10 @@
         <v>1</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F17+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -3935,11 +4007,10 @@
         <v>1</v>
       </c>
       <c r="F19" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F18+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -3950,17 +4021,16 @@
         <v>26</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F19+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -3971,17 +4041,16 @@
         <v>27</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
       </c>
       <c r="F21" s="1">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F20+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -3992,17 +4061,16 @@
         <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
       </c>
       <c r="F22" s="1">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F21+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -4013,17 +4081,16 @@
         <v>29</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F22+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -4034,17 +4101,16 @@
         <v>30</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F23+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -4055,17 +4121,16 @@
         <v>31</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
       </c>
       <c r="F25" s="1">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F24+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -4076,17 +4141,16 @@
         <v>32</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F25+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -4097,17 +4161,16 @@
         <v>33</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
       </c>
       <c r="F27" s="1">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F26+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -4118,17 +4181,16 @@
         <v>34</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
       </c>
       <c r="F28" s="1">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F27+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -4139,17 +4201,16 @@
         <v>35</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F28+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -4160,17 +4221,16 @@
         <v>36</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F29+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -4181,17 +4241,16 @@
         <v>37</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+        <f>F30+1</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -4199,7 +4258,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>43</v>
@@ -4211,7 +4270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -4219,7 +4278,7 @@
         <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>43</v>
@@ -4231,7 +4290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -4239,10 +4298,10 @@
         <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E34" s="1">
         <v>0</v>
@@ -4251,7 +4310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -4259,10 +4318,10 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E35" s="1">
         <v>0</v>
@@ -4271,7 +4330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -4279,10 +4338,10 @@
         <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E36" s="1">
         <v>0</v>
@@ -4291,7 +4350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -4299,7 +4358,7 @@
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>43</v>
@@ -4311,7 +4370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -4319,7 +4378,7 @@
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>43</v>
@@ -4331,7 +4390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -4339,7 +4398,7 @@
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>43</v>
@@ -4351,7 +4410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -4359,7 +4418,7 @@
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>43</v>
@@ -4371,7 +4430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -4379,10 +4438,10 @@
         <v>9</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E41" s="1">
         <v>0</v>
@@ -4391,7 +4450,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -4399,10 +4458,10 @@
         <v>9</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E42" s="1">
         <v>0</v>
@@ -4411,7 +4470,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -4419,10 +4478,10 @@
         <v>9</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
@@ -4431,7 +4490,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -4439,10 +4498,10 @@
         <v>5</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E44" s="1">
         <v>0</v>
@@ -4451,7 +4510,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -4459,10 +4518,10 @@
         <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E45" s="1">
         <v>0</v>
@@ -4471,7 +4530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -4479,10 +4538,10 @@
         <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E46" s="1">
         <v>0</v>
@@ -4491,7 +4550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -4499,7 +4558,7 @@
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>43</v>
@@ -4511,7 +4570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -4519,7 +4578,7 @@
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>43</v>
@@ -4531,7 +4590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -4539,7 +4598,7 @@
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>43</v>
@@ -4551,7 +4610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -4559,7 +4618,7 @@
         <v>9</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>43</v>
@@ -4571,7 +4630,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -4579,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>43</v>
@@ -4591,7 +4650,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -4599,7 +4658,7 @@
         <v>9</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>43</v>
@@ -4611,7 +4670,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -4619,7 +4678,7 @@
         <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>43</v>
@@ -4631,7 +4690,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -4639,7 +4698,7 @@
         <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>43</v>
@@ -4651,7 +4710,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -4659,7 +4718,7 @@
         <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>43</v>
@@ -4671,7 +4730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -4679,7 +4738,7 @@
         <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>43</v>
@@ -4691,7 +4750,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -4699,7 +4758,7 @@
         <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>43</v>
@@ -4711,7 +4770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -4719,7 +4778,7 @@
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>43</v>
@@ -4731,7 +4790,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -4739,7 +4798,7 @@
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>43</v>
@@ -4751,7 +4810,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -4759,7 +4818,7 @@
         <v>7</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>43</v>
@@ -4771,7 +4830,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -4779,7 +4838,7 @@
         <v>9</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>43</v>
@@ -4791,7 +4850,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -4799,7 +4858,7 @@
         <v>9</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>43</v>
@@ -4811,7 +4870,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -4819,7 +4878,7 @@
         <v>9</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>43</v>
@@ -4831,7 +4890,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -4839,7 +4898,7 @@
         <v>5</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>43</v>
@@ -4851,7 +4910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -4859,7 +4918,7 @@
         <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>43</v>
@@ -4871,7 +4930,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -4879,7 +4938,7 @@
         <v>5</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>43</v>
@@ -4891,7 +4950,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -4899,7 +4958,7 @@
         <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>43</v>
@@ -4911,7 +4970,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -4919,7 +4978,7 @@
         <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>43</v>
@@ -4931,7 +4990,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -4939,7 +4998,7 @@
         <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>43</v>
@@ -4951,7 +5010,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -4959,7 +5018,7 @@
         <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>43</v>
@@ -4971,7 +5030,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -4979,7 +5038,7 @@
         <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>43</v>
@@ -4991,7 +5050,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -4999,7 +5058,7 @@
         <v>9</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>43</v>
@@ -5011,7 +5070,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -5019,7 +5078,7 @@
         <v>9</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>43</v>
@@ -5031,7 +5090,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -5039,7 +5098,7 @@
         <v>9</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>43</v>
@@ -5051,335 +5110,339 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
       <c r="E75" s="1">
         <v>0</v>
       </c>
-      <c r="F75" s="10"/>
-    </row>
-    <row r="76" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F75" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
       <c r="E76" s="1">
         <v>0</v>
       </c>
-      <c r="F76" s="10"/>
-    </row>
-    <row r="77" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F76" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
       <c r="E77" s="1">
         <v>0</v>
       </c>
-      <c r="F77" s="10"/>
-    </row>
-    <row r="78" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F77" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
       <c r="E78" s="1">
         <v>0</v>
       </c>
-      <c r="F78" s="10"/>
-    </row>
-    <row r="79" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F78" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
       <c r="E79" s="1">
         <v>0</v>
       </c>
-      <c r="F79" s="10"/>
-    </row>
-    <row r="80" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F79" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
       <c r="E80" s="1">
         <v>0</v>
       </c>
-      <c r="F80" s="10"/>
-    </row>
-    <row r="81" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F80" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="1">
         <v>80</v>
       </c>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
       <c r="E81" s="1">
         <v>0</v>
       </c>
-      <c r="F81" s="10"/>
-    </row>
-    <row r="82" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F81" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="1">
         <v>81</v>
       </c>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
       <c r="E82" s="1">
         <v>0</v>
       </c>
-      <c r="F82" s="10"/>
-    </row>
-    <row r="83" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F82" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="1">
         <v>82</v>
       </c>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
       <c r="E83" s="1">
         <v>0</v>
       </c>
-      <c r="F83" s="10"/>
-    </row>
-    <row r="84" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F83" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="1">
         <v>83</v>
       </c>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
       <c r="E84" s="1">
         <v>0</v>
       </c>
-      <c r="F84" s="10"/>
-    </row>
-    <row r="85" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F84" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="1">
         <v>84</v>
       </c>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
       <c r="E85" s="1">
         <v>0</v>
       </c>
-      <c r="F85" s="10"/>
-    </row>
-    <row r="86" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F85" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="1">
         <v>85</v>
       </c>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
       <c r="E86" s="1">
         <v>0</v>
       </c>
-      <c r="F86" s="10"/>
-    </row>
-    <row r="87" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F86" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="1">
         <v>86</v>
       </c>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
       <c r="E87" s="1">
         <v>0</v>
       </c>
-      <c r="F87" s="10"/>
-    </row>
-    <row r="88" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F87" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="1">
         <v>87</v>
       </c>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
       <c r="E88" s="1">
         <v>0</v>
       </c>
-      <c r="F88" s="10"/>
-    </row>
-    <row r="89" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F88" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="1">
         <v>88</v>
       </c>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
       <c r="E89" s="1">
         <v>0</v>
       </c>
-      <c r="F89" s="10"/>
-    </row>
-    <row r="90" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F89" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="1">
         <v>89</v>
       </c>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
       <c r="E90" s="1">
         <v>0</v>
       </c>
-      <c r="F90" s="10"/>
-    </row>
-    <row r="91" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F90" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="1">
         <v>90</v>
       </c>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
       <c r="E91" s="1">
         <v>0</v>
       </c>
-      <c r="F91" s="10"/>
-    </row>
-    <row r="92" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F91" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="1">
         <v>91</v>
       </c>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
       <c r="E92" s="1">
         <v>0</v>
       </c>
-      <c r="F92" s="10"/>
-    </row>
-    <row r="93" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F92" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="1">
         <v>92</v>
       </c>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
       <c r="E93" s="1">
         <v>0</v>
       </c>
-      <c r="F93" s="10"/>
-    </row>
-    <row r="94" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F93" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="1">
         <v>93</v>
       </c>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
       <c r="E94" s="1">
         <v>0</v>
       </c>
-      <c r="F94" s="10"/>
-    </row>
-    <row r="95" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F94" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="1">
         <v>94</v>
       </c>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
       <c r="E95" s="1">
         <v>0</v>
       </c>
-      <c r="F95" s="10"/>
-    </row>
-    <row r="96" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F95" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="1">
         <v>95</v>
       </c>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
       <c r="E96" s="1">
         <v>0</v>
       </c>
-      <c r="F96" s="10"/>
-    </row>
-    <row r="97" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F96" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="1">
         <v>96</v>
       </c>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
       <c r="E97" s="1">
         <v>0</v>
       </c>
-      <c r="F97" s="10"/>
-    </row>
-    <row r="98" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F97" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="1">
         <v>97</v>
       </c>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
       <c r="E98" s="1">
         <v>0</v>
       </c>
-      <c r="F98" s="10"/>
-    </row>
-    <row r="99" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F98" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="1">
         <v>98</v>
       </c>
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
       <c r="E99" s="1">
         <v>0</v>
       </c>
-      <c r="F99" s="10"/>
-    </row>
-    <row r="100" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F99" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="1">
         <v>99</v>
       </c>
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
       <c r="E100" s="1">
         <v>0</v>
       </c>
-      <c r="F100" s="10"/>
-    </row>
-    <row r="101" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F100" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="19.5">
       <c r="A101" s="1">
         <v>100</v>
       </c>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
       <c r="E101" s="1">
         <v>0</v>
       </c>
-      <c r="F101" s="10"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F101" s="7"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="17.25">
       <c r="A102" s="1">
-        <f t="shared" ref="A66:A102" si="1">A101+1</f>
-        <v>101</v>
-      </c>
+        <f>A101+1</f>
+      </c>
+      <c r="B102" s="8"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="9"/>
+      <c r="F102" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5387,22 +5450,27 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:K31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="13.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="53.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="3" width="46.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5425,7 +5493,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -5448,7 +5516,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -5471,7 +5539,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -5494,7 +5562,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -5517,7 +5585,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -5540,7 +5608,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -5563,7 +5631,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -5586,7 +5654,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -5609,7 +5677,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -5632,7 +5700,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -5655,7 +5723,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -5678,10 +5746,9 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1">
-        <f t="shared" ref="A13:A31" si="0">A12+1</f>
-        <v>12</v>
+        <f>A12+1</f>
       </c>
       <c r="B13" s="2" t="s">
         <v>9</v>
@@ -5702,10 +5769,9 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f>A13+1</f>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
@@ -5726,10 +5792,9 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1">
-        <f t="shared" si="0"/>
-        <v>14</v>
+        <f>A14+1</f>
       </c>
       <c r="B15" s="2" t="s">
         <v>7</v>
@@ -5750,10 +5815,9 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <f>A15+1</f>
       </c>
       <c r="B16" s="2" t="s">
         <v>9</v>
@@ -5774,10 +5838,9 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>A16+1</f>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
@@ -5798,10 +5861,9 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="1">
-        <f t="shared" si="0"/>
-        <v>17</v>
+        <f>A17+1</f>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
@@ -5822,10 +5884,9 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <f>A18+1</f>
       </c>
       <c r="B19" s="2" t="s">
         <v>9</v>
@@ -5846,10 +5907,9 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="1">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <f>A19+1</f>
       </c>
       <c r="B20" s="2" t="s">
         <v>5</v>
@@ -5870,10 +5930,9 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="1">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f>A20+1</f>
       </c>
       <c r="B21" s="2" t="s">
         <v>7</v>
@@ -5894,10 +5953,9 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1">
-        <f t="shared" si="0"/>
-        <v>21</v>
+        <f>A21+1</f>
       </c>
       <c r="B22" s="2" t="s">
         <v>9</v>
@@ -5918,10 +5976,9 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1">
-        <f t="shared" si="0"/>
-        <v>22</v>
+        <f>A22+1</f>
       </c>
       <c r="B23" s="2" t="s">
         <v>5</v>
@@ -5942,10 +5999,9 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="1">
-        <f t="shared" si="0"/>
-        <v>23</v>
+        <f>A23+1</f>
       </c>
       <c r="B24" s="2" t="s">
         <v>7</v>
@@ -5966,10 +6022,9 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1">
-        <f t="shared" si="0"/>
-        <v>24</v>
+        <f>A24+1</f>
       </c>
       <c r="B25" s="2" t="s">
         <v>9</v>
@@ -5990,10 +6045,9 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="1">
-        <f t="shared" si="0"/>
-        <v>25</v>
+        <f>A25+1</f>
       </c>
       <c r="B26" s="2" t="s">
         <v>5</v>
@@ -6014,10 +6068,9 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="1">
-        <f t="shared" si="0"/>
-        <v>26</v>
+        <f>A26+1</f>
       </c>
       <c r="B27" s="2" t="s">
         <v>7</v>
@@ -6038,10 +6091,9 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="1">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <f>A27+1</f>
       </c>
       <c r="B28" s="2" t="s">
         <v>9</v>
@@ -6062,10 +6114,9 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="1">
-        <f t="shared" si="0"/>
-        <v>28</v>
+        <f>A28+1</f>
       </c>
       <c r="B29" s="2" t="s">
         <v>5</v>
@@ -6086,10 +6137,9 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="1">
-        <f t="shared" si="0"/>
-        <v>29</v>
+        <f>A29+1</f>
       </c>
       <c r="B30" s="2" t="s">
         <v>7</v>
@@ -6110,10 +6160,9 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="1">
-        <f t="shared" si="0"/>
-        <v>30</v>
+        <f>A30+1</f>
       </c>
       <c r="B31" s="2" t="s">
         <v>9</v>
@@ -6140,12 +6189,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
